--- a/Individual Treasure Averages.xlsx
+++ b/Individual Treasure Averages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hanks\DnD-Homebrew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23890694-66BF-4645-B3AC-2352F74DDBA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFBDA5E-DBE5-487D-B058-4811C8D4A518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="25820" windowHeight="13900" tabRatio="616" firstSheet="1" activeTab="3" xr2:uid="{5E3698F5-01A8-41EE-A738-BAB99CC962C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="616" firstSheet="1" activeTab="3" xr2:uid="{5E3698F5-01A8-41EE-A738-BAB99CC962C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Individual Treasure(2024 Less)" sheetId="8" r:id="rId1"/>
@@ -873,11 +873,20 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -888,16 +897,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -905,9 +908,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3242,20 +3242,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
       <c r="Z1" s="39"/>
       <c r="AA1" s="39"/>
       <c r="AB1" s="39"/>
@@ -3297,10 +3297,10 @@
       <c r="AD2" s="37"/>
     </row>
     <row r="3" spans="1:30" s="14" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="69"/>
+      <c r="B3" s="77"/>
       <c r="C3" s="21">
         <v>3</v>
       </c>
@@ -3495,18 +3495,18 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="74"/>
+      <c r="B10" s="72"/>
       <c r="C10" s="33">
         <f>'Individual Treasure(2014)'!B3</f>
         <v>1.0794007754789445</v>
       </c>
-      <c r="D10" s="75" t="s">
+      <c r="D10" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="76"/>
+      <c r="E10" s="70"/>
       <c r="F10" s="34">
         <f>SUMPRODUCT(C5:C9,F5:F9)</f>
         <v>1</v>
@@ -3532,20 +3532,20 @@
       <c r="AD10" s="13"/>
     </row>
     <row r="11" spans="1:30" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="79" t="s">
+      <c r="A11" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
       <c r="Z11" s="39"/>
       <c r="AA11" s="39"/>
       <c r="AB11" s="39"/>
@@ -3553,14 +3553,14 @@
       <c r="AD11" s="39"/>
     </row>
     <row r="12" spans="1:30" ht="26" x14ac:dyDescent="0.6">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="78"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="79"/>
       <c r="G12" s="37"/>
       <c r="H12" s="37"/>
       <c r="I12" s="37"/>
@@ -3587,18 +3587,18 @@
       <c r="AD12" s="37"/>
     </row>
     <row r="13" spans="1:30" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="69"/>
+      <c r="B13" s="77"/>
       <c r="C13" s="21">
         <v>3</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="71"/>
-      <c r="F13" s="72"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="75"/>
       <c r="G13" s="38"/>
       <c r="H13" s="38"/>
       <c r="I13" s="36"/>
@@ -3755,18 +3755,18 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="74"/>
+      <c r="B20" s="72"/>
       <c r="C20" s="33">
         <f>'Individual Treasure(2014)'!B4</f>
         <v>1.6717350674697367</v>
       </c>
-      <c r="D20" s="75" t="s">
+      <c r="D20" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="76"/>
+      <c r="E20" s="70"/>
       <c r="F20" s="34">
         <f>SUMPRODUCT(C15:C19,F15:F19)</f>
         <v>1.6750000000000003</v>
@@ -3775,64 +3775,64 @@
       <c r="K20" s="13"/>
     </row>
     <row r="21" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="79" t="s">
+      <c r="A21" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="79"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="68"/>
     </row>
     <row r="22" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="77" t="s">
+      <c r="B22" s="78"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="78"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="78"/>
+      <c r="J22" s="78"/>
+      <c r="K22" s="78"/>
+      <c r="L22" s="79"/>
     </row>
     <row r="23" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="69"/>
+      <c r="B23" s="77"/>
       <c r="C23" s="21">
         <v>3</v>
       </c>
-      <c r="D23" s="70" t="s">
+      <c r="D23" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="71"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="68" t="s">
+      <c r="E23" s="74"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H23" s="69"/>
+      <c r="H23" s="77"/>
       <c r="I23" s="21">
         <v>3</v>
       </c>
-      <c r="J23" s="70" t="s">
+      <c r="J23" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K23" s="71"/>
-      <c r="L23" s="72"/>
+      <c r="K23" s="74"/>
+      <c r="L23" s="75"/>
     </row>
     <row r="24" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="42" t="s">
@@ -4095,98 +4095,98 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="73" t="s">
+      <c r="A30" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="74"/>
+      <c r="B30" s="72"/>
       <c r="C30" s="33">
         <f>'Individual Treasure(2014)'!B5</f>
         <v>2.5891199999999999</v>
       </c>
-      <c r="D30" s="75" t="s">
+      <c r="D30" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="76"/>
+      <c r="E30" s="70"/>
       <c r="F30" s="34">
         <f>SUMPRODUCT(C25:C29,F25:F29)</f>
         <v>2.5750000000000002</v>
       </c>
-      <c r="G30" s="73" t="s">
+      <c r="G30" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H30" s="74"/>
+      <c r="H30" s="72"/>
       <c r="I30" s="33">
         <f>'Individual Treasure(2014)'!B5</f>
         <v>2.5891199999999999</v>
       </c>
-      <c r="J30" s="75" t="s">
+      <c r="J30" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K30" s="76"/>
+      <c r="K30" s="70"/>
       <c r="L30" s="34">
         <f>SUMPRODUCT(I25:I29,L25:L29)</f>
         <v>2.5499999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="79" t="s">
+      <c r="A31" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="79"/>
-      <c r="K31" s="79"/>
-      <c r="L31" s="79"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="68"/>
+      <c r="L31" s="68"/>
     </row>
     <row r="32" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="77" t="s">
+      <c r="A32" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="77"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="77" t="s">
+      <c r="B32" s="78"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="79"/>
+      <c r="G32" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="77"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="78"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="78"/>
+      <c r="K32" s="78"/>
+      <c r="L32" s="79"/>
     </row>
     <row r="33" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="68" t="s">
+      <c r="A33" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B33" s="69"/>
+      <c r="B33" s="77"/>
       <c r="C33" s="21">
         <v>3</v>
       </c>
-      <c r="D33" s="70" t="s">
+      <c r="D33" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="71"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="68" t="s">
+      <c r="E33" s="74"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="69"/>
+      <c r="H33" s="77"/>
       <c r="I33" s="21">
         <v>3</v>
       </c>
-      <c r="J33" s="70" t="s">
+      <c r="J33" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K33" s="71"/>
-      <c r="L33" s="72"/>
+      <c r="K33" s="74"/>
+      <c r="L33" s="75"/>
     </row>
     <row r="34" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="42" t="s">
@@ -4449,98 +4449,98 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40" s="73" t="s">
+      <c r="A40" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="74"/>
+      <c r="B40" s="72"/>
       <c r="C40" s="33">
         <f>'Individual Treasure(2014)'!B6</f>
         <v>4.0099310619512103</v>
       </c>
-      <c r="D40" s="75" t="s">
+      <c r="D40" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E40" s="76"/>
+      <c r="E40" s="70"/>
       <c r="F40" s="34">
         <f>SUMPRODUCT(C35:C39,F35:F39)</f>
         <v>4.05</v>
       </c>
-      <c r="G40" s="73" t="s">
+      <c r="G40" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H40" s="74"/>
+      <c r="H40" s="72"/>
       <c r="I40" s="33">
         <f>'Individual Treasure(2014)'!B6</f>
         <v>4.0099310619512103</v>
       </c>
-      <c r="J40" s="75" t="s">
+      <c r="J40" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K40" s="76"/>
+      <c r="K40" s="70"/>
       <c r="L40" s="34">
         <f>SUMPRODUCT(I35:I39,L35:L39)</f>
         <v>8.25</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="79" t="s">
+      <c r="A41" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="B41" s="79"/>
-      <c r="C41" s="79"/>
-      <c r="D41" s="79"/>
-      <c r="E41" s="79"/>
-      <c r="F41" s="79"/>
-      <c r="G41" s="79"/>
-      <c r="H41" s="79"/>
-      <c r="I41" s="79"/>
-      <c r="J41" s="79"/>
-      <c r="K41" s="79"/>
-      <c r="L41" s="79"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
     </row>
     <row r="42" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="77" t="s">
+      <c r="A42" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="77"/>
-      <c r="C42" s="77"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="77" t="s">
+      <c r="B42" s="78"/>
+      <c r="C42" s="78"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="79"/>
+      <c r="G42" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="H42" s="77"/>
-      <c r="I42" s="77"/>
-      <c r="J42" s="77"/>
-      <c r="K42" s="77"/>
-      <c r="L42" s="78"/>
+      <c r="H42" s="78"/>
+      <c r="I42" s="78"/>
+      <c r="J42" s="78"/>
+      <c r="K42" s="78"/>
+      <c r="L42" s="79"/>
     </row>
     <row r="43" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="68" t="s">
+      <c r="A43" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B43" s="69"/>
+      <c r="B43" s="77"/>
       <c r="C43" s="21">
         <v>3</v>
       </c>
-      <c r="D43" s="70" t="s">
+      <c r="D43" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E43" s="71"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="68" t="s">
+      <c r="E43" s="74"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H43" s="69"/>
+      <c r="H43" s="77"/>
       <c r="I43" s="21">
         <v>3</v>
       </c>
-      <c r="J43" s="70" t="s">
+      <c r="J43" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K43" s="71"/>
-      <c r="L43" s="72"/>
+      <c r="K43" s="74"/>
+      <c r="L43" s="75"/>
     </row>
     <row r="44" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="42" t="s">
@@ -4586,21 +4586,21 @@
         <v>4</v>
       </c>
       <c r="B45" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C45" s="31">
         <f>((B45-A45+1)*0.05)</f>
-        <v>0.05</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="D45" s="18">
         <v>1</v>
       </c>
       <c r="E45" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="19">
         <f>D45*E45</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="43">
         <f>I43+1</f>
@@ -4627,24 +4627,24 @@
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="43">
         <f>B45+1</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B46" s="8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C46" s="31">
         <f>((B46-A46+1)*0.05)</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D46" s="18">
         <v>2</v>
       </c>
       <c r="E46" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="19">
         <f>D46*E46</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G46" s="43">
         <f>H45+1</f>
@@ -4671,14 +4671,14 @@
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="43">
         <f>B46+1</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B47" s="8">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C47" s="31">
         <f>((B47-A47+1)*0.05)</f>
-        <v>0.2</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="D47" s="18">
         <v>3</v>
@@ -4715,24 +4715,24 @@
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="43">
         <f>B47+1</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B48" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C48" s="31">
         <f>((B48-A48+1)*0.05)</f>
-        <v>0.35000000000000003</v>
+        <v>0.2</v>
       </c>
       <c r="D48" s="18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E48" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F48" s="19">
         <f>D48*E48</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G48" s="43">
         <f>H47+1</f>
@@ -4759,7 +4759,7 @@
     <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="43">
         <f>B48+1</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B49" s="44">
         <f>20+C43</f>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="C49" s="31">
         <f>((B49-A49+1)*0.05)</f>
-        <v>0.30000000000000004</v>
+        <v>0.1</v>
       </c>
       <c r="D49" s="20">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E49" s="28">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F49" s="22">
         <f>D49*E49</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G49" s="43">
         <f>H48+1</f>
@@ -4803,103 +4803,103 @@
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A50" s="73" t="s">
+      <c r="A50" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="74"/>
+      <c r="B50" s="72"/>
       <c r="C50" s="33">
         <f>'Individual Treasure(2014)'!B7</f>
         <v>6.2104294592761873</v>
       </c>
-      <c r="D50" s="75" t="s">
+      <c r="D50" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E50" s="76"/>
+      <c r="E50" s="70"/>
       <c r="F50" s="34">
         <f>SUMPRODUCT(C45:C49,F45:F49)</f>
-        <v>6.2000000000000011</v>
-      </c>
-      <c r="G50" s="73" t="s">
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="G50" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H50" s="74"/>
+      <c r="H50" s="72"/>
       <c r="I50" s="33">
         <f>'Individual Treasure(2014)'!B16</f>
         <v>318.40814976470659</v>
       </c>
-      <c r="J50" s="75" t="s">
+      <c r="J50" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K50" s="76"/>
+      <c r="K50" s="70"/>
       <c r="L50" s="34">
         <f>SUMPRODUCT(I45:I49,L45:L49)</f>
         <v>5.7</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="79" t="s">
+      <c r="A51" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="79"/>
-      <c r="C51" s="79"/>
-      <c r="D51" s="79"/>
-      <c r="E51" s="79"/>
-      <c r="F51" s="79"/>
-      <c r="G51" s="79"/>
-      <c r="H51" s="79"/>
-      <c r="I51" s="79"/>
-      <c r="J51" s="79"/>
-      <c r="K51" s="79"/>
-      <c r="L51" s="79"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="68"/>
+      <c r="E51" s="68"/>
+      <c r="F51" s="68"/>
+      <c r="G51" s="68"/>
+      <c r="H51" s="68"/>
+      <c r="I51" s="68"/>
+      <c r="J51" s="68"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="68"/>
     </row>
     <row r="52" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="77" t="s">
+      <c r="A52" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="B52" s="77"/>
-      <c r="C52" s="77"/>
-      <c r="D52" s="77"/>
-      <c r="E52" s="77"/>
-      <c r="F52" s="78"/>
-      <c r="G52" s="77" t="s">
+      <c r="B52" s="78"/>
+      <c r="C52" s="78"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="78"/>
+      <c r="F52" s="79"/>
+      <c r="G52" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="H52" s="77"/>
-      <c r="I52" s="77"/>
-      <c r="J52" s="77"/>
-      <c r="K52" s="77"/>
-      <c r="L52" s="78"/>
+      <c r="H52" s="78"/>
+      <c r="I52" s="78"/>
+      <c r="J52" s="78"/>
+      <c r="K52" s="78"/>
+      <c r="L52" s="79"/>
     </row>
     <row r="53" spans="1:16" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="68" t="s">
+      <c r="A53" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B53" s="69"/>
+      <c r="B53" s="77"/>
       <c r="C53" s="21">
         <v>3</v>
       </c>
-      <c r="D53" s="70" t="s">
+      <c r="D53" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E53" s="71"/>
-      <c r="F53" s="72"/>
-      <c r="G53" s="68" t="s">
+      <c r="E53" s="74"/>
+      <c r="F53" s="75"/>
+      <c r="G53" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H53" s="69"/>
+      <c r="H53" s="77"/>
       <c r="I53" s="21">
         <v>3</v>
       </c>
-      <c r="J53" s="70" t="s">
+      <c r="J53" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K53" s="71"/>
-      <c r="L53" s="72"/>
-      <c r="M53" s="70" t="s">
+      <c r="K53" s="74"/>
+      <c r="L53" s="75"/>
+      <c r="M53" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="N53" s="71"/>
-      <c r="O53" s="72"/>
+      <c r="N53" s="74"/>
+      <c r="O53" s="75"/>
       <c r="P53" s="46"/>
     </row>
     <row r="54" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -4958,21 +4958,21 @@
         <v>4</v>
       </c>
       <c r="B55" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="31">
         <f>((B55-A55+1)*0.05)</f>
-        <v>0.15000000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="D55" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F55" s="19">
         <f>D55*E55</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55" s="43">
         <f>I53+1</f>
@@ -5013,24 +5013,24 @@
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="43">
         <f>B55+1</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B56" s="8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C56" s="31">
         <f>((B56-A56+1)*0.05)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D56" s="18">
+        <v>3</v>
+      </c>
+      <c r="E56" s="8">
         <v>2</v>
-      </c>
-      <c r="E56" s="8">
-        <v>5</v>
       </c>
       <c r="F56" s="19">
         <f>D56*E56</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G56" s="43">
         <f>H55+1</f>
@@ -5071,24 +5071,24 @@
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="43">
         <f>B56+1</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B57" s="8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C57" s="31">
         <f>((B57-A57+1)*0.05)</f>
         <v>0.35000000000000003</v>
       </c>
       <c r="D57" s="18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E57" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F57" s="19">
         <f>D57*E57</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G57" s="43">
         <f>H56+1</f>
@@ -5129,24 +5129,24 @@
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="43">
         <f>B57+1</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B58" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C58" s="31">
         <f>((B58-A58+1)*0.05)</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D58" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="8">
         <v>10</v>
       </c>
       <c r="F58" s="19">
         <f>D58*E58</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G58" s="43">
         <f>H57+1</f>
@@ -5187,7 +5187,7 @@
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="43">
         <f>B58+1</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B59" s="44">
         <f>20+C53</f>
@@ -5195,17 +5195,17 @@
       </c>
       <c r="C59" s="31">
         <f>((B59-A59+1)*0.05)</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D59" s="20">
-        <v>3</v>
-      </c>
-      <c r="E59" s="28">
+        <v>2</v>
+      </c>
+      <c r="E59" s="8">
         <v>10</v>
       </c>
       <c r="F59" s="22">
         <f>D59*E59</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G59" s="43">
         <f>H58+1</f>
@@ -5245,42 +5245,42 @@
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A60" s="73" t="s">
+      <c r="A60" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B60" s="74"/>
+      <c r="B60" s="72"/>
       <c r="C60" s="33">
         <f>'Individual Treasure(2014)'!B8</f>
         <v>9.6184780917100969</v>
       </c>
-      <c r="D60" s="75" t="s">
+      <c r="D60" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E60" s="76"/>
+      <c r="E60" s="70"/>
       <c r="F60" s="34">
         <f>SUMPRODUCT(C55:C59,F55:F59)</f>
-        <v>14</v>
-      </c>
-      <c r="G60" s="73" t="s">
+        <v>9.6000000000000014</v>
+      </c>
+      <c r="G60" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H60" s="74"/>
+      <c r="H60" s="72"/>
       <c r="I60" s="33">
         <f>'Individual Treasure(2014)'!B8</f>
         <v>9.6184780917100969</v>
       </c>
-      <c r="J60" s="75" t="s">
+      <c r="J60" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K60" s="76"/>
+      <c r="K60" s="70"/>
       <c r="L60" s="34">
         <f>SUMPRODUCT(I55:I59,L55:L59)</f>
         <v>6.5</v>
       </c>
-      <c r="M60" s="75" t="s">
+      <c r="M60" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="N60" s="76"/>
+      <c r="N60" s="70"/>
       <c r="O60" s="34">
         <f>SUMPRODUCT(I55:I59,O55:O59)</f>
         <v>3.45</v>
@@ -5291,44 +5291,44 @@
       </c>
     </row>
     <row r="61" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="79" t="s">
+      <c r="A61" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="79"/>
-      <c r="C61" s="79"/>
-      <c r="D61" s="79"/>
-      <c r="E61" s="79"/>
-      <c r="F61" s="79"/>
-      <c r="G61" s="79"/>
-      <c r="H61" s="79"/>
-      <c r="I61" s="79"/>
-      <c r="J61" s="79"/>
-      <c r="K61" s="79"/>
-      <c r="L61" s="79"/>
+      <c r="B61" s="68"/>
+      <c r="C61" s="68"/>
+      <c r="D61" s="68"/>
+      <c r="E61" s="68"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="68"/>
+      <c r="H61" s="68"/>
+      <c r="I61" s="68"/>
+      <c r="J61" s="68"/>
+      <c r="K61" s="68"/>
+      <c r="L61" s="68"/>
     </row>
     <row r="62" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="77" t="s">
+      <c r="A62" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="77"/>
-      <c r="C62" s="77"/>
-      <c r="D62" s="77"/>
-      <c r="E62" s="77"/>
-      <c r="F62" s="78"/>
+      <c r="B62" s="78"/>
+      <c r="C62" s="78"/>
+      <c r="D62" s="78"/>
+      <c r="E62" s="78"/>
+      <c r="F62" s="79"/>
     </row>
     <row r="63" spans="1:16" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="68" t="s">
+      <c r="A63" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B63" s="69"/>
+      <c r="B63" s="77"/>
       <c r="C63" s="21">
         <v>3</v>
       </c>
-      <c r="D63" s="70" t="s">
+      <c r="D63" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E63" s="71"/>
-      <c r="F63" s="72"/>
+      <c r="E63" s="74"/>
+      <c r="F63" s="75"/>
     </row>
     <row r="64" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="42" t="s">
@@ -5356,96 +5356,96 @@
         <v>4</v>
       </c>
       <c r="B65" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C65" s="31">
         <f>((B65-A65+1)*0.05)</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D65" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E65" s="8">
         <v>5</v>
       </c>
       <c r="F65" s="19">
         <f>D65*E65</f>
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="43">
         <f>B65+1</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B66" s="8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C66" s="31">
         <f>((B66-A66+1)*0.05)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D66" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F66" s="19">
         <f>D66*E66</f>
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="43">
         <f>B66+1</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B67" s="8">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C67" s="31">
         <f>((B67-A67+1)*0.05)</f>
         <v>0.35000000000000003</v>
       </c>
       <c r="D67" s="18">
+        <v>3</v>
+      </c>
+      <c r="E67" s="8">
         <v>5</v>
-      </c>
-      <c r="E67" s="8">
-        <v>10</v>
       </c>
       <c r="F67" s="19">
         <f>D67*E67</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="43">
         <f>B67+1</f>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B68" s="8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C68" s="31">
         <f>((B68-A68+1)*0.05)</f>
-        <v>0.15000000000000002</v>
+        <v>0.25</v>
       </c>
       <c r="D68" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" s="8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F68" s="19">
         <f>D68*E68</f>
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="43">
         <f>B68+1</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B69" s="44">
         <f>20+C63</f>
@@ -5453,101 +5453,101 @@
       </c>
       <c r="C69" s="31">
         <f>((B69-A69+1)*0.05)</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D69" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E69" s="28">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F69" s="22">
         <f>D69*E69</f>
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A70" s="73" t="s">
+      <c r="A70" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B70" s="74"/>
+      <c r="B70" s="72"/>
       <c r="C70" s="33">
         <f>'Individual Treasure(2014)'!B9</f>
         <v>14.89673482443669</v>
       </c>
-      <c r="D70" s="75" t="s">
+      <c r="D70" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E70" s="76"/>
+      <c r="E70" s="70"/>
       <c r="F70" s="34">
         <f>SUMPRODUCT(C65:C69,F65:F69)</f>
-        <v>44</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="79" t="s">
+      <c r="A71" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B71" s="79"/>
-      <c r="C71" s="79"/>
-      <c r="D71" s="79"/>
-      <c r="E71" s="79"/>
-      <c r="F71" s="79"/>
-      <c r="G71" s="79"/>
-      <c r="H71" s="79"/>
-      <c r="I71" s="79"/>
-      <c r="J71" s="79"/>
-      <c r="K71" s="79"/>
-      <c r="L71" s="79"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="68"/>
+      <c r="D71" s="68"/>
+      <c r="E71" s="68"/>
+      <c r="F71" s="68"/>
+      <c r="G71" s="68"/>
+      <c r="H71" s="68"/>
+      <c r="I71" s="68"/>
+      <c r="J71" s="68"/>
+      <c r="K71" s="68"/>
+      <c r="L71" s="68"/>
     </row>
     <row r="72" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="77" t="s">
+      <c r="A72" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="B72" s="77"/>
-      <c r="C72" s="77"/>
-      <c r="D72" s="77"/>
-      <c r="E72" s="77"/>
-      <c r="F72" s="78"/>
-      <c r="G72" s="77" t="s">
+      <c r="B72" s="78"/>
+      <c r="C72" s="78"/>
+      <c r="D72" s="78"/>
+      <c r="E72" s="78"/>
+      <c r="F72" s="79"/>
+      <c r="G72" s="78" t="s">
         <v>98</v>
       </c>
-      <c r="H72" s="77"/>
-      <c r="I72" s="77"/>
-      <c r="J72" s="77"/>
-      <c r="K72" s="77"/>
-      <c r="L72" s="78"/>
+      <c r="H72" s="78"/>
+      <c r="I72" s="78"/>
+      <c r="J72" s="78"/>
+      <c r="K72" s="78"/>
+      <c r="L72" s="79"/>
     </row>
     <row r="73" spans="1:16" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A73" s="68" t="s">
+      <c r="A73" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B73" s="69"/>
+      <c r="B73" s="77"/>
       <c r="C73" s="21">
         <v>5</v>
       </c>
-      <c r="D73" s="70" t="s">
+      <c r="D73" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E73" s="71"/>
-      <c r="F73" s="72"/>
-      <c r="G73" s="68" t="s">
+      <c r="E73" s="74"/>
+      <c r="F73" s="75"/>
+      <c r="G73" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H73" s="69"/>
+      <c r="H73" s="77"/>
       <c r="I73" s="21">
         <v>5</v>
       </c>
-      <c r="J73" s="70" t="s">
+      <c r="J73" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K73" s="71"/>
-      <c r="L73" s="72"/>
-      <c r="M73" s="70" t="s">
+      <c r="K73" s="74"/>
+      <c r="L73" s="75"/>
+      <c r="M73" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="N73" s="71"/>
-      <c r="O73" s="72"/>
+      <c r="N73" s="74"/>
+      <c r="O73" s="75"/>
       <c r="P73" s="46"/>
     </row>
     <row r="74" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -5893,42 +5893,42 @@
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B80" s="74"/>
+      <c r="B80" s="72"/>
       <c r="C80" s="33">
         <f>'Individual Treasure(2014)'!B10</f>
         <v>23.071499078512772</v>
       </c>
-      <c r="D80" s="75" t="s">
+      <c r="D80" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E80" s="76"/>
+      <c r="E80" s="70"/>
       <c r="F80" s="34">
         <f>SUMPRODUCT(C75:C79,F75:F79)</f>
         <v>44</v>
       </c>
-      <c r="G80" s="73" t="s">
+      <c r="G80" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H80" s="74"/>
+      <c r="H80" s="72"/>
       <c r="I80" s="33">
         <f>'Individual Treasure(2014)'!B10</f>
         <v>23.071499078512772</v>
       </c>
-      <c r="J80" s="75" t="s">
+      <c r="J80" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K80" s="76"/>
+      <c r="K80" s="70"/>
       <c r="L80" s="34">
         <f>SUMPRODUCT(I75:I79,L75:L79)</f>
         <v>16.5</v>
       </c>
-      <c r="M80" s="75" t="s">
+      <c r="M80" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="N80" s="76"/>
+      <c r="N80" s="70"/>
       <c r="O80" s="34">
         <f>SUMPRODUCT(I75:I79,O75:O79)</f>
         <v>7.3500000000000005</v>
@@ -5939,69 +5939,69 @@
       </c>
     </row>
     <row r="81" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A81" s="79" t="s">
+      <c r="A81" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B81" s="79"/>
-      <c r="C81" s="79"/>
-      <c r="D81" s="79"/>
-      <c r="E81" s="79"/>
-      <c r="F81" s="79"/>
-      <c r="G81" s="79"/>
-      <c r="H81" s="79"/>
-      <c r="I81" s="79"/>
-      <c r="J81" s="79"/>
-      <c r="K81" s="79"/>
-      <c r="L81" s="79"/>
+      <c r="B81" s="68"/>
+      <c r="C81" s="68"/>
+      <c r="D81" s="68"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="68"/>
+      <c r="H81" s="68"/>
+      <c r="I81" s="68"/>
+      <c r="J81" s="68"/>
+      <c r="K81" s="68"/>
+      <c r="L81" s="68"/>
     </row>
     <row r="82" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="77" t="s">
+      <c r="A82" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="B82" s="77"/>
-      <c r="C82" s="77"/>
-      <c r="D82" s="77"/>
-      <c r="E82" s="77"/>
-      <c r="F82" s="78"/>
-      <c r="G82" s="77" t="s">
+      <c r="B82" s="78"/>
+      <c r="C82" s="78"/>
+      <c r="D82" s="78"/>
+      <c r="E82" s="78"/>
+      <c r="F82" s="79"/>
+      <c r="G82" s="78" t="s">
         <v>99</v>
       </c>
-      <c r="H82" s="77"/>
-      <c r="I82" s="77"/>
-      <c r="J82" s="77"/>
-      <c r="K82" s="77"/>
-      <c r="L82" s="78"/>
+      <c r="H82" s="78"/>
+      <c r="I82" s="78"/>
+      <c r="J82" s="78"/>
+      <c r="K82" s="78"/>
+      <c r="L82" s="79"/>
     </row>
     <row r="83" spans="1:16" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A83" s="68" t="s">
+      <c r="A83" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B83" s="69"/>
+      <c r="B83" s="77"/>
       <c r="C83" s="21">
         <v>5</v>
       </c>
-      <c r="D83" s="70" t="s">
+      <c r="D83" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E83" s="71"/>
-      <c r="F83" s="72"/>
-      <c r="G83" s="68" t="s">
+      <c r="E83" s="74"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H83" s="69"/>
+      <c r="H83" s="77"/>
       <c r="I83" s="21">
         <v>5</v>
       </c>
-      <c r="J83" s="70" t="s">
+      <c r="J83" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K83" s="71"/>
-      <c r="L83" s="72"/>
-      <c r="M83" s="70" t="s">
+      <c r="K83" s="74"/>
+      <c r="L83" s="75"/>
+      <c r="M83" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="N83" s="71"/>
-      <c r="O83" s="72"/>
+      <c r="N83" s="74"/>
+      <c r="O83" s="75"/>
       <c r="P83" s="46"/>
     </row>
     <row r="84" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -6347,42 +6347,42 @@
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A90" s="73" t="s">
+      <c r="A90" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B90" s="74"/>
+      <c r="B90" s="72"/>
       <c r="C90" s="33">
         <f>'Individual Treasure(2014)'!B11</f>
         <v>35.732264553480377</v>
       </c>
-      <c r="D90" s="75" t="s">
+      <c r="D90" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E90" s="76"/>
+      <c r="E90" s="70"/>
       <c r="F90" s="34">
         <f>SUMPRODUCT(C85:C89,F85:F89)</f>
         <v>65.5</v>
       </c>
-      <c r="G90" s="73" t="s">
+      <c r="G90" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H90" s="74"/>
+      <c r="H90" s="72"/>
       <c r="I90" s="33">
         <f>'Individual Treasure(2014)'!B11</f>
         <v>35.732264553480377</v>
       </c>
-      <c r="J90" s="75" t="s">
+      <c r="J90" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K90" s="76"/>
+      <c r="K90" s="70"/>
       <c r="L90" s="34">
         <f>SUMPRODUCT(I85:I89,L85:L89)</f>
         <v>45</v>
       </c>
-      <c r="M90" s="75" t="s">
+      <c r="M90" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="N90" s="76"/>
+      <c r="N90" s="70"/>
       <c r="O90" s="34">
         <f>SUMPRODUCT(I85:I89,O85:O89)</f>
         <v>10.650000000000002</v>
@@ -6393,64 +6393,64 @@
       </c>
     </row>
     <row r="91" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A91" s="79" t="s">
+      <c r="A91" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="B91" s="79"/>
-      <c r="C91" s="79"/>
-      <c r="D91" s="79"/>
-      <c r="E91" s="79"/>
-      <c r="F91" s="79"/>
-      <c r="G91" s="79"/>
-      <c r="H91" s="79"/>
-      <c r="I91" s="79"/>
-      <c r="J91" s="79"/>
-      <c r="K91" s="79"/>
-      <c r="L91" s="79"/>
+      <c r="B91" s="68"/>
+      <c r="C91" s="68"/>
+      <c r="D91" s="68"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="68"/>
+      <c r="G91" s="68"/>
+      <c r="H91" s="68"/>
+      <c r="I91" s="68"/>
+      <c r="J91" s="68"/>
+      <c r="K91" s="68"/>
+      <c r="L91" s="68"/>
     </row>
     <row r="92" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="77" t="s">
+      <c r="A92" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B92" s="77"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
-      <c r="E92" s="77"/>
-      <c r="F92" s="78"/>
-      <c r="G92" s="77" t="s">
+      <c r="B92" s="78"/>
+      <c r="C92" s="78"/>
+      <c r="D92" s="78"/>
+      <c r="E92" s="78"/>
+      <c r="F92" s="79"/>
+      <c r="G92" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="H92" s="77"/>
-      <c r="I92" s="77"/>
-      <c r="J92" s="77"/>
-      <c r="K92" s="77"/>
-      <c r="L92" s="78"/>
+      <c r="H92" s="78"/>
+      <c r="I92" s="78"/>
+      <c r="J92" s="78"/>
+      <c r="K92" s="78"/>
+      <c r="L92" s="79"/>
     </row>
     <row r="93" spans="1:16" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="68" t="s">
+      <c r="A93" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B93" s="69"/>
+      <c r="B93" s="77"/>
       <c r="C93" s="21">
         <v>5</v>
       </c>
-      <c r="D93" s="70" t="s">
+      <c r="D93" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E93" s="71"/>
-      <c r="F93" s="72"/>
-      <c r="G93" s="68" t="s">
+      <c r="E93" s="74"/>
+      <c r="F93" s="75"/>
+      <c r="G93" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H93" s="69"/>
+      <c r="H93" s="77"/>
       <c r="I93" s="21">
         <v>5</v>
       </c>
-      <c r="J93" s="70" t="s">
+      <c r="J93" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K93" s="71"/>
-      <c r="L93" s="72"/>
+      <c r="K93" s="74"/>
+      <c r="L93" s="75"/>
     </row>
     <row r="94" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94" s="42" t="s">
@@ -6713,103 +6713,103 @@
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A100" s="73" t="s">
+      <c r="A100" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B100" s="74"/>
+      <c r="B100" s="72"/>
       <c r="C100" s="33">
         <f>'Individual Treasure(2014)'!B12</f>
         <v>55.340778931397217</v>
       </c>
-      <c r="D100" s="75" t="s">
+      <c r="D100" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E100" s="76"/>
+      <c r="E100" s="70"/>
       <c r="F100" s="34">
         <f>SUMPRODUCT(C95:C99,F95:F99)</f>
         <v>82.25</v>
       </c>
-      <c r="G100" s="73" t="s">
+      <c r="G100" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H100" s="74"/>
+      <c r="H100" s="72"/>
       <c r="I100" s="33">
         <f>'Individual Treasure(2014)'!B12</f>
         <v>55.340778931397217</v>
       </c>
-      <c r="J100" s="75" t="s">
+      <c r="J100" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K100" s="76"/>
+      <c r="K100" s="70"/>
       <c r="L100" s="34">
         <f>SUMPRODUCT(I95:I99,L95:L99)</f>
         <v>56.25</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A101" s="79" t="s">
+      <c r="A101" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="B101" s="79"/>
-      <c r="C101" s="79"/>
-      <c r="D101" s="79"/>
-      <c r="E101" s="79"/>
-      <c r="F101" s="79"/>
-      <c r="G101" s="79"/>
-      <c r="H101" s="79"/>
-      <c r="I101" s="79"/>
-      <c r="J101" s="79"/>
-      <c r="K101" s="79"/>
-      <c r="L101" s="79"/>
+      <c r="B101" s="68"/>
+      <c r="C101" s="68"/>
+      <c r="D101" s="68"/>
+      <c r="E101" s="68"/>
+      <c r="F101" s="68"/>
+      <c r="G101" s="68"/>
+      <c r="H101" s="68"/>
+      <c r="I101" s="68"/>
+      <c r="J101" s="68"/>
+      <c r="K101" s="68"/>
+      <c r="L101" s="68"/>
     </row>
     <row r="102" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" s="77" t="s">
+      <c r="A102" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="B102" s="77"/>
-      <c r="C102" s="77"/>
-      <c r="D102" s="77"/>
-      <c r="E102" s="77"/>
-      <c r="F102" s="78"/>
-      <c r="G102" s="77" t="s">
+      <c r="B102" s="78"/>
+      <c r="C102" s="78"/>
+      <c r="D102" s="78"/>
+      <c r="E102" s="78"/>
+      <c r="F102" s="79"/>
+      <c r="G102" s="78" t="s">
         <v>100</v>
       </c>
-      <c r="H102" s="77"/>
-      <c r="I102" s="77"/>
-      <c r="J102" s="77"/>
-      <c r="K102" s="77"/>
-      <c r="L102" s="78"/>
+      <c r="H102" s="78"/>
+      <c r="I102" s="78"/>
+      <c r="J102" s="78"/>
+      <c r="K102" s="78"/>
+      <c r="L102" s="79"/>
     </row>
     <row r="103" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="68" t="s">
+      <c r="A103" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B103" s="69"/>
+      <c r="B103" s="77"/>
       <c r="C103" s="21">
         <v>5</v>
       </c>
-      <c r="D103" s="70" t="s">
+      <c r="D103" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E103" s="71"/>
-      <c r="F103" s="72"/>
-      <c r="G103" s="68" t="s">
+      <c r="E103" s="74"/>
+      <c r="F103" s="75"/>
+      <c r="G103" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H103" s="69"/>
+      <c r="H103" s="77"/>
       <c r="I103" s="21">
         <v>5</v>
       </c>
-      <c r="J103" s="70" t="s">
+      <c r="J103" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K103" s="71"/>
-      <c r="L103" s="72"/>
-      <c r="M103" s="70" t="s">
+      <c r="K103" s="74"/>
+      <c r="L103" s="75"/>
+      <c r="M103" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="N103" s="71"/>
-      <c r="O103" s="72"/>
+      <c r="N103" s="74"/>
+      <c r="O103" s="75"/>
       <c r="P103" s="46"/>
     </row>
     <row r="104" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -7155,42 +7155,42 @@
       </c>
     </row>
     <row r="110" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="73" t="s">
+      <c r="A110" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B110" s="74"/>
+      <c r="B110" s="72"/>
       <c r="C110" s="33">
         <f>'Individual Treasure(2014)'!B13</f>
         <v>85.709703849023938</v>
       </c>
-      <c r="D110" s="75" t="s">
+      <c r="D110" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E110" s="76"/>
+      <c r="E110" s="70"/>
       <c r="F110" s="34">
         <f>SUMPRODUCT(C105:C109,F105:F109)</f>
         <v>85.5</v>
       </c>
-      <c r="G110" s="73" t="s">
+      <c r="G110" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H110" s="74"/>
+      <c r="H110" s="72"/>
       <c r="I110" s="33">
         <f>'Individual Treasure(2014)'!B13</f>
         <v>85.709703849023938</v>
       </c>
-      <c r="J110" s="75" t="s">
+      <c r="J110" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K110" s="76"/>
+      <c r="K110" s="70"/>
       <c r="L110" s="34">
         <f>SUMPRODUCT(I105:I109,L105:L109)</f>
         <v>97.5</v>
       </c>
-      <c r="M110" s="75" t="s">
+      <c r="M110" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="N110" s="76"/>
+      <c r="N110" s="70"/>
       <c r="O110" s="34">
         <f>SUMPRODUCT(I105:I109,O105:O109)</f>
         <v>29.75</v>
@@ -7201,64 +7201,64 @@
       </c>
     </row>
     <row r="111" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A111" s="79" t="s">
+      <c r="A111" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="B111" s="79"/>
-      <c r="C111" s="79"/>
-      <c r="D111" s="79"/>
-      <c r="E111" s="79"/>
-      <c r="F111" s="79"/>
-      <c r="G111" s="79"/>
-      <c r="H111" s="79"/>
-      <c r="I111" s="79"/>
-      <c r="J111" s="79"/>
-      <c r="K111" s="79"/>
-      <c r="L111" s="79"/>
+      <c r="B111" s="68"/>
+      <c r="C111" s="68"/>
+      <c r="D111" s="68"/>
+      <c r="E111" s="68"/>
+      <c r="F111" s="68"/>
+      <c r="G111" s="68"/>
+      <c r="H111" s="68"/>
+      <c r="I111" s="68"/>
+      <c r="J111" s="68"/>
+      <c r="K111" s="68"/>
+      <c r="L111" s="68"/>
     </row>
     <row r="112" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" s="77" t="s">
+      <c r="A112" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="B112" s="77"/>
-      <c r="C112" s="77"/>
-      <c r="D112" s="77"/>
-      <c r="E112" s="77"/>
-      <c r="F112" s="78"/>
-      <c r="G112" s="77" t="s">
+      <c r="B112" s="78"/>
+      <c r="C112" s="78"/>
+      <c r="D112" s="78"/>
+      <c r="E112" s="78"/>
+      <c r="F112" s="79"/>
+      <c r="G112" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="H112" s="77"/>
-      <c r="I112" s="77"/>
-      <c r="J112" s="77"/>
-      <c r="K112" s="77"/>
-      <c r="L112" s="78"/>
+      <c r="H112" s="78"/>
+      <c r="I112" s="78"/>
+      <c r="J112" s="78"/>
+      <c r="K112" s="78"/>
+      <c r="L112" s="79"/>
     </row>
     <row r="113" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A113" s="68" t="s">
+      <c r="A113" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B113" s="69"/>
+      <c r="B113" s="77"/>
       <c r="C113" s="21">
         <v>5</v>
       </c>
-      <c r="D113" s="70" t="s">
+      <c r="D113" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E113" s="71"/>
-      <c r="F113" s="72"/>
-      <c r="G113" s="68" t="s">
+      <c r="E113" s="74"/>
+      <c r="F113" s="75"/>
+      <c r="G113" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H113" s="69"/>
+      <c r="H113" s="77"/>
       <c r="I113" s="21">
         <v>5</v>
       </c>
-      <c r="J113" s="70" t="s">
+      <c r="J113" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K113" s="71"/>
-      <c r="L113" s="72"/>
+      <c r="K113" s="74"/>
+      <c r="L113" s="75"/>
     </row>
     <row r="114" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A114" s="42" t="s">
@@ -7521,98 +7521,98 @@
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A120" s="73" t="s">
+      <c r="A120" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B120" s="74"/>
+      <c r="B120" s="72"/>
       <c r="C120" s="33">
         <f>'Individual Treasure(2014)'!B14</f>
         <v>132.7439453462336</v>
       </c>
-      <c r="D120" s="75" t="s">
+      <c r="D120" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E120" s="76"/>
+      <c r="E120" s="70"/>
       <c r="F120" s="34">
         <f>SUMPRODUCT(C115:C119,F115:F119)</f>
         <v>132.5</v>
       </c>
-      <c r="G120" s="73" t="s">
+      <c r="G120" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H120" s="74"/>
+      <c r="H120" s="72"/>
       <c r="I120" s="33">
         <f>'Individual Treasure(2014)'!B14</f>
         <v>132.7439453462336</v>
       </c>
-      <c r="J120" s="75" t="s">
+      <c r="J120" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K120" s="76"/>
+      <c r="K120" s="70"/>
       <c r="L120" s="34">
         <f>SUMPRODUCT(I115:I119,L115:L119)</f>
         <v>202.5</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A121" s="79" t="s">
+      <c r="A121" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="B121" s="79"/>
-      <c r="C121" s="79"/>
-      <c r="D121" s="79"/>
-      <c r="E121" s="79"/>
-      <c r="F121" s="79"/>
-      <c r="G121" s="79"/>
-      <c r="H121" s="79"/>
-      <c r="I121" s="79"/>
-      <c r="J121" s="79"/>
-      <c r="K121" s="79"/>
-      <c r="L121" s="79"/>
+      <c r="B121" s="68"/>
+      <c r="C121" s="68"/>
+      <c r="D121" s="68"/>
+      <c r="E121" s="68"/>
+      <c r="F121" s="68"/>
+      <c r="G121" s="68"/>
+      <c r="H121" s="68"/>
+      <c r="I121" s="68"/>
+      <c r="J121" s="68"/>
+      <c r="K121" s="68"/>
+      <c r="L121" s="68"/>
     </row>
     <row r="122" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" s="77" t="s">
+      <c r="A122" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="B122" s="77"/>
-      <c r="C122" s="77"/>
-      <c r="D122" s="77"/>
-      <c r="E122" s="77"/>
-      <c r="F122" s="78"/>
-      <c r="G122" s="77" t="s">
+      <c r="B122" s="78"/>
+      <c r="C122" s="78"/>
+      <c r="D122" s="78"/>
+      <c r="E122" s="78"/>
+      <c r="F122" s="79"/>
+      <c r="G122" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="H122" s="77"/>
-      <c r="I122" s="77"/>
-      <c r="J122" s="77"/>
-      <c r="K122" s="77"/>
-      <c r="L122" s="78"/>
+      <c r="H122" s="78"/>
+      <c r="I122" s="78"/>
+      <c r="J122" s="78"/>
+      <c r="K122" s="78"/>
+      <c r="L122" s="79"/>
     </row>
     <row r="123" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="68" t="s">
+      <c r="A123" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B123" s="69"/>
+      <c r="B123" s="77"/>
       <c r="C123" s="21">
         <v>5</v>
       </c>
-      <c r="D123" s="70" t="s">
+      <c r="D123" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E123" s="71"/>
-      <c r="F123" s="72"/>
-      <c r="G123" s="68" t="s">
+      <c r="E123" s="74"/>
+      <c r="F123" s="75"/>
+      <c r="G123" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H123" s="69"/>
+      <c r="H123" s="77"/>
       <c r="I123" s="21">
         <v>5</v>
       </c>
-      <c r="J123" s="70" t="s">
+      <c r="J123" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K123" s="71"/>
-      <c r="L123" s="72"/>
+      <c r="K123" s="74"/>
+      <c r="L123" s="75"/>
     </row>
     <row r="124" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A124" s="42" t="s">
@@ -7875,98 +7875,98 @@
       </c>
     </row>
     <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="73" t="s">
+      <c r="A130" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B130" s="74"/>
+      <c r="B130" s="72"/>
       <c r="C130" s="33">
         <f>'Individual Treasure(2014)'!B15</f>
         <v>205.58879840633722</v>
       </c>
-      <c r="D130" s="75" t="s">
+      <c r="D130" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E130" s="76"/>
+      <c r="E130" s="70"/>
       <c r="F130" s="34">
         <f>SUMPRODUCT(C125:C129,F125:F129)</f>
         <v>305</v>
       </c>
-      <c r="G130" s="73" t="s">
+      <c r="G130" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H130" s="74"/>
+      <c r="H130" s="72"/>
       <c r="I130" s="33">
         <f>'Individual Treasure(2014)'!B15</f>
         <v>205.58879840633722</v>
       </c>
-      <c r="J130" s="75" t="s">
+      <c r="J130" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K130" s="76"/>
+      <c r="K130" s="70"/>
       <c r="L130" s="34">
         <f>SUMPRODUCT(I125:I129,L125:L129)</f>
         <v>205.5</v>
       </c>
     </row>
     <row r="131" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A131" s="79" t="s">
+      <c r="A131" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="B131" s="79"/>
-      <c r="C131" s="79"/>
-      <c r="D131" s="79"/>
-      <c r="E131" s="79"/>
-      <c r="F131" s="79"/>
-      <c r="G131" s="79"/>
-      <c r="H131" s="79"/>
-      <c r="I131" s="79"/>
-      <c r="J131" s="79"/>
-      <c r="K131" s="79"/>
-      <c r="L131" s="79"/>
+      <c r="B131" s="68"/>
+      <c r="C131" s="68"/>
+      <c r="D131" s="68"/>
+      <c r="E131" s="68"/>
+      <c r="F131" s="68"/>
+      <c r="G131" s="68"/>
+      <c r="H131" s="68"/>
+      <c r="I131" s="68"/>
+      <c r="J131" s="68"/>
+      <c r="K131" s="68"/>
+      <c r="L131" s="68"/>
     </row>
     <row r="132" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A132" s="77" t="s">
+      <c r="A132" s="78" t="s">
         <v>75</v>
       </c>
-      <c r="B132" s="77"/>
-      <c r="C132" s="77"/>
-      <c r="D132" s="77"/>
-      <c r="E132" s="77"/>
-      <c r="F132" s="78"/>
-      <c r="G132" s="77" t="s">
+      <c r="B132" s="78"/>
+      <c r="C132" s="78"/>
+      <c r="D132" s="78"/>
+      <c r="E132" s="78"/>
+      <c r="F132" s="79"/>
+      <c r="G132" s="78" t="s">
         <v>75</v>
       </c>
-      <c r="H132" s="77"/>
-      <c r="I132" s="77"/>
-      <c r="J132" s="77"/>
-      <c r="K132" s="77"/>
-      <c r="L132" s="78"/>
+      <c r="H132" s="78"/>
+      <c r="I132" s="78"/>
+      <c r="J132" s="78"/>
+      <c r="K132" s="78"/>
+      <c r="L132" s="79"/>
     </row>
     <row r="133" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A133" s="68" t="s">
+      <c r="A133" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B133" s="69"/>
+      <c r="B133" s="77"/>
       <c r="C133" s="21">
         <v>7</v>
       </c>
-      <c r="D133" s="70" t="s">
+      <c r="D133" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E133" s="71"/>
-      <c r="F133" s="72"/>
-      <c r="G133" s="68" t="s">
+      <c r="E133" s="74"/>
+      <c r="F133" s="75"/>
+      <c r="G133" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H133" s="69"/>
+      <c r="H133" s="77"/>
       <c r="I133" s="21">
         <v>7</v>
       </c>
-      <c r="J133" s="70" t="s">
+      <c r="J133" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K133" s="71"/>
-      <c r="L133" s="72"/>
+      <c r="K133" s="74"/>
+      <c r="L133" s="75"/>
     </row>
     <row r="134" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A134" s="42" t="s">
@@ -8229,78 +8229,78 @@
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A140" s="73" t="s">
+      <c r="A140" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B140" s="74"/>
+      <c r="B140" s="72"/>
       <c r="C140" s="33">
         <f>'Individual Treasure(2014)'!B16</f>
         <v>318.40814976470659</v>
       </c>
-      <c r="D140" s="75" t="s">
+      <c r="D140" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E140" s="76"/>
+      <c r="E140" s="70"/>
       <c r="F140" s="34">
         <f>SUMPRODUCT(C135:C139,F135:F139)</f>
         <v>460</v>
       </c>
-      <c r="G140" s="73" t="s">
+      <c r="G140" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H140" s="74"/>
+      <c r="H140" s="72"/>
       <c r="I140" s="33">
         <f>'Individual Treasure(2014)'!B16</f>
         <v>318.40814976470659</v>
       </c>
-      <c r="J140" s="75" t="s">
+      <c r="J140" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K140" s="76"/>
+      <c r="K140" s="70"/>
       <c r="L140" s="34">
         <f>SUMPRODUCT(I135:I139,L135:L139)</f>
         <v>505</v>
       </c>
     </row>
     <row r="141" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A141" s="79" t="s">
+      <c r="A141" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="B141" s="79"/>
-      <c r="C141" s="79"/>
-      <c r="D141" s="79"/>
-      <c r="E141" s="79"/>
-      <c r="F141" s="79"/>
-      <c r="G141" s="79"/>
-      <c r="H141" s="79"/>
-      <c r="I141" s="79"/>
-      <c r="J141" s="79"/>
-      <c r="K141" s="79"/>
-      <c r="L141" s="79"/>
+      <c r="B141" s="68"/>
+      <c r="C141" s="68"/>
+      <c r="D141" s="68"/>
+      <c r="E141" s="68"/>
+      <c r="F141" s="68"/>
+      <c r="G141" s="68"/>
+      <c r="H141" s="68"/>
+      <c r="I141" s="68"/>
+      <c r="J141" s="68"/>
+      <c r="K141" s="68"/>
+      <c r="L141" s="68"/>
     </row>
     <row r="142" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A142" s="77" t="s">
+      <c r="A142" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="B142" s="77"/>
-      <c r="C142" s="77"/>
-      <c r="D142" s="77"/>
-      <c r="E142" s="77"/>
-      <c r="F142" s="78"/>
+      <c r="B142" s="78"/>
+      <c r="C142" s="78"/>
+      <c r="D142" s="78"/>
+      <c r="E142" s="78"/>
+      <c r="F142" s="79"/>
     </row>
     <row r="143" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="68" t="s">
+      <c r="A143" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B143" s="69"/>
+      <c r="B143" s="77"/>
       <c r="C143" s="21">
         <v>7</v>
       </c>
-      <c r="D143" s="70" t="s">
+      <c r="D143" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E143" s="71"/>
-      <c r="F143" s="72"/>
+      <c r="E143" s="74"/>
+      <c r="F143" s="75"/>
     </row>
     <row r="144" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A144" s="42" t="s">
@@ -8439,82 +8439,82 @@
       </c>
     </row>
     <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A150" s="73" t="s">
+      <c r="A150" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B150" s="74"/>
+      <c r="B150" s="72"/>
       <c r="C150" s="33">
         <f>'Individual Treasure(2014)'!B17</f>
         <v>493.13849111663814</v>
       </c>
-      <c r="D150" s="75" t="s">
+      <c r="D150" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E150" s="76"/>
+      <c r="E150" s="70"/>
       <c r="F150" s="34">
         <f>SUMPRODUCT(C145:C149,F145:F149)</f>
         <v>495</v>
       </c>
     </row>
     <row r="151" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A151" s="79" t="s">
+      <c r="A151" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="B151" s="79"/>
-      <c r="C151" s="79"/>
-      <c r="D151" s="79"/>
-      <c r="E151" s="79"/>
-      <c r="F151" s="79"/>
-      <c r="G151" s="79"/>
-      <c r="H151" s="79"/>
-      <c r="I151" s="79"/>
-      <c r="J151" s="79"/>
-      <c r="K151" s="79"/>
-      <c r="L151" s="79"/>
+      <c r="B151" s="68"/>
+      <c r="C151" s="68"/>
+      <c r="D151" s="68"/>
+      <c r="E151" s="68"/>
+      <c r="F151" s="68"/>
+      <c r="G151" s="68"/>
+      <c r="H151" s="68"/>
+      <c r="I151" s="68"/>
+      <c r="J151" s="68"/>
+      <c r="K151" s="68"/>
+      <c r="L151" s="68"/>
     </row>
     <row r="152" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A152" s="77" t="s">
+      <c r="A152" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="B152" s="77"/>
-      <c r="C152" s="77"/>
-      <c r="D152" s="77"/>
-      <c r="E152" s="77"/>
-      <c r="F152" s="78"/>
-      <c r="G152" s="77" t="s">
+      <c r="B152" s="78"/>
+      <c r="C152" s="78"/>
+      <c r="D152" s="78"/>
+      <c r="E152" s="78"/>
+      <c r="F152" s="79"/>
+      <c r="G152" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="H152" s="77"/>
-      <c r="I152" s="77"/>
-      <c r="J152" s="77"/>
-      <c r="K152" s="77"/>
-      <c r="L152" s="78"/>
+      <c r="H152" s="78"/>
+      <c r="I152" s="78"/>
+      <c r="J152" s="78"/>
+      <c r="K152" s="78"/>
+      <c r="L152" s="79"/>
     </row>
     <row r="153" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A153" s="68" t="s">
+      <c r="A153" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B153" s="69"/>
+      <c r="B153" s="77"/>
       <c r="C153" s="21">
         <v>7</v>
       </c>
-      <c r="D153" s="70" t="s">
+      <c r="D153" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E153" s="71"/>
-      <c r="F153" s="72"/>
-      <c r="G153" s="68" t="s">
+      <c r="E153" s="74"/>
+      <c r="F153" s="75"/>
+      <c r="G153" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H153" s="69"/>
+      <c r="H153" s="77"/>
       <c r="I153" s="21">
         <v>7</v>
       </c>
-      <c r="J153" s="70" t="s">
+      <c r="J153" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K153" s="71"/>
-      <c r="L153" s="72"/>
+      <c r="K153" s="74"/>
+      <c r="L153" s="75"/>
     </row>
     <row r="154" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A154" s="42" t="s">
@@ -8777,78 +8777,78 @@
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A160" s="73" t="s">
+      <c r="A160" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B160" s="74"/>
+      <c r="B160" s="72"/>
       <c r="C160" s="33">
         <f>'Individual Treasure(2014)'!B18</f>
         <v>763.75423053869986</v>
       </c>
-      <c r="D160" s="75" t="s">
+      <c r="D160" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E160" s="76"/>
+      <c r="E160" s="70"/>
       <c r="F160" s="34">
         <f>SUMPRODUCT(C155:C159,F155:F159)</f>
         <v>1025</v>
       </c>
-      <c r="G160" s="73" t="s">
+      <c r="G160" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H160" s="74"/>
+      <c r="H160" s="72"/>
       <c r="I160" s="33">
         <f>'Individual Treasure(2014)'!B18</f>
         <v>763.75423053869986</v>
       </c>
-      <c r="J160" s="75" t="s">
+      <c r="J160" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K160" s="76"/>
+      <c r="K160" s="70"/>
       <c r="L160" s="34">
         <f>SUMPRODUCT(I155:I159,L155:L159)</f>
         <v>770</v>
       </c>
     </row>
     <row r="161" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A161" s="79" t="s">
+      <c r="A161" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B161" s="79"/>
-      <c r="C161" s="79"/>
-      <c r="D161" s="79"/>
-      <c r="E161" s="79"/>
-      <c r="F161" s="79"/>
-      <c r="G161" s="79"/>
-      <c r="H161" s="79"/>
-      <c r="I161" s="79"/>
-      <c r="J161" s="79"/>
-      <c r="K161" s="79"/>
-      <c r="L161" s="79"/>
+      <c r="B161" s="68"/>
+      <c r="C161" s="68"/>
+      <c r="D161" s="68"/>
+      <c r="E161" s="68"/>
+      <c r="F161" s="68"/>
+      <c r="G161" s="68"/>
+      <c r="H161" s="68"/>
+      <c r="I161" s="68"/>
+      <c r="J161" s="68"/>
+      <c r="K161" s="68"/>
+      <c r="L161" s="68"/>
     </row>
     <row r="162" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A162" s="77" t="s">
+      <c r="A162" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="B162" s="77"/>
-      <c r="C162" s="77"/>
-      <c r="D162" s="77"/>
-      <c r="E162" s="77"/>
-      <c r="F162" s="78"/>
+      <c r="B162" s="78"/>
+      <c r="C162" s="78"/>
+      <c r="D162" s="78"/>
+      <c r="E162" s="78"/>
+      <c r="F162" s="79"/>
     </row>
     <row r="163" spans="1:16" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A163" s="68" t="s">
+      <c r="A163" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B163" s="69"/>
+      <c r="B163" s="77"/>
       <c r="C163" s="21">
         <v>7</v>
       </c>
-      <c r="D163" s="70" t="s">
+      <c r="D163" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E163" s="71"/>
-      <c r="F163" s="72"/>
+      <c r="E163" s="74"/>
+      <c r="F163" s="75"/>
     </row>
     <row r="164" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A164" s="42" t="s">
@@ -8987,87 +8987,87 @@
       </c>
     </row>
     <row r="170" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A170" s="73" t="s">
+      <c r="A170" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B170" s="74"/>
+      <c r="B170" s="72"/>
       <c r="C170" s="33">
         <f>'Individual Treasure(2014)'!B19</f>
         <v>1182.8736453829017</v>
       </c>
-      <c r="D170" s="75" t="s">
+      <c r="D170" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E170" s="76"/>
+      <c r="E170" s="70"/>
       <c r="F170" s="34">
         <f>SUMPRODUCT(C165:C169,F165:F169)</f>
         <v>1122.5</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A171" s="79" t="s">
+      <c r="A171" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="B171" s="79"/>
-      <c r="C171" s="79"/>
-      <c r="D171" s="79"/>
-      <c r="E171" s="79"/>
-      <c r="F171" s="79"/>
-      <c r="G171" s="79"/>
-      <c r="H171" s="79"/>
-      <c r="I171" s="79"/>
-      <c r="J171" s="79"/>
-      <c r="K171" s="79"/>
-      <c r="L171" s="79"/>
+      <c r="B171" s="68"/>
+      <c r="C171" s="68"/>
+      <c r="D171" s="68"/>
+      <c r="E171" s="68"/>
+      <c r="F171" s="68"/>
+      <c r="G171" s="68"/>
+      <c r="H171" s="68"/>
+      <c r="I171" s="68"/>
+      <c r="J171" s="68"/>
+      <c r="K171" s="68"/>
+      <c r="L171" s="68"/>
     </row>
     <row r="172" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A172" s="77" t="s">
+      <c r="A172" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="B172" s="77"/>
-      <c r="C172" s="77"/>
-      <c r="D172" s="77"/>
-      <c r="E172" s="77"/>
-      <c r="F172" s="78"/>
-      <c r="G172" s="77" t="s">
+      <c r="B172" s="78"/>
+      <c r="C172" s="78"/>
+      <c r="D172" s="78"/>
+      <c r="E172" s="78"/>
+      <c r="F172" s="79"/>
+      <c r="G172" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="H172" s="77"/>
-      <c r="I172" s="77"/>
-      <c r="J172" s="77"/>
-      <c r="K172" s="77"/>
-      <c r="L172" s="78"/>
+      <c r="H172" s="78"/>
+      <c r="I172" s="78"/>
+      <c r="J172" s="78"/>
+      <c r="K172" s="78"/>
+      <c r="L172" s="79"/>
     </row>
     <row r="173" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A173" s="68" t="s">
+      <c r="A173" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B173" s="69"/>
+      <c r="B173" s="77"/>
       <c r="C173" s="21">
         <v>7</v>
       </c>
-      <c r="D173" s="70" t="s">
+      <c r="D173" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E173" s="71"/>
-      <c r="F173" s="72"/>
-      <c r="G173" s="68" t="s">
+      <c r="E173" s="74"/>
+      <c r="F173" s="75"/>
+      <c r="G173" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H173" s="69"/>
+      <c r="H173" s="77"/>
       <c r="I173" s="21">
         <v>5</v>
       </c>
-      <c r="J173" s="70" t="s">
+      <c r="J173" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K173" s="71"/>
-      <c r="L173" s="72"/>
-      <c r="M173" s="70" t="s">
+      <c r="K173" s="74"/>
+      <c r="L173" s="75"/>
+      <c r="M173" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="N173" s="71"/>
-      <c r="O173" s="72"/>
+      <c r="N173" s="74"/>
+      <c r="O173" s="75"/>
       <c r="P173" s="46"/>
     </row>
     <row r="174" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -9413,42 +9413,42 @@
       </c>
     </row>
     <row r="180" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="73" t="s">
+      <c r="A180" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B180" s="74"/>
+      <c r="B180" s="72"/>
       <c r="C180" s="33">
         <f>'Individual Treasure(2014)'!B20</f>
         <v>1831.989932094441</v>
       </c>
-      <c r="D180" s="75" t="s">
+      <c r="D180" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E180" s="76"/>
+      <c r="E180" s="70"/>
       <c r="F180" s="34">
         <f>SUMPRODUCT(C175:C179,F175:F179)</f>
         <v>3550</v>
       </c>
-      <c r="G180" s="73" t="s">
+      <c r="G180" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H180" s="74"/>
+      <c r="H180" s="72"/>
       <c r="I180" s="33">
         <f>'Individual Treasure(2014)'!B20</f>
         <v>1831.989932094441</v>
       </c>
-      <c r="J180" s="75" t="s">
+      <c r="J180" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K180" s="76"/>
+      <c r="K180" s="70"/>
       <c r="L180" s="34">
         <f>SUMPRODUCT(I175:I179,L175:L179)</f>
         <v>1225</v>
       </c>
-      <c r="M180" s="75" t="s">
+      <c r="M180" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="N180" s="76"/>
+      <c r="N180" s="70"/>
       <c r="O180" s="34">
         <f>SUMPRODUCT(I175:I179,O175:O179)</f>
         <v>660</v>
@@ -9459,44 +9459,44 @@
       </c>
     </row>
     <row r="181" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A181" s="79" t="s">
+      <c r="A181" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="B181" s="79"/>
-      <c r="C181" s="79"/>
-      <c r="D181" s="79"/>
-      <c r="E181" s="79"/>
-      <c r="F181" s="79"/>
-      <c r="G181" s="79"/>
-      <c r="H181" s="79"/>
-      <c r="I181" s="79"/>
-      <c r="J181" s="79"/>
-      <c r="K181" s="79"/>
-      <c r="L181" s="79"/>
+      <c r="B181" s="68"/>
+      <c r="C181" s="68"/>
+      <c r="D181" s="68"/>
+      <c r="E181" s="68"/>
+      <c r="F181" s="68"/>
+      <c r="G181" s="68"/>
+      <c r="H181" s="68"/>
+      <c r="I181" s="68"/>
+      <c r="J181" s="68"/>
+      <c r="K181" s="68"/>
+      <c r="L181" s="68"/>
     </row>
     <row r="182" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A182" s="77" t="s">
+      <c r="A182" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="B182" s="77"/>
-      <c r="C182" s="77"/>
-      <c r="D182" s="77"/>
-      <c r="E182" s="77"/>
-      <c r="F182" s="78"/>
+      <c r="B182" s="78"/>
+      <c r="C182" s="78"/>
+      <c r="D182" s="78"/>
+      <c r="E182" s="78"/>
+      <c r="F182" s="79"/>
     </row>
     <row r="183" spans="1:16" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="68" t="s">
+      <c r="A183" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B183" s="69"/>
+      <c r="B183" s="77"/>
       <c r="C183" s="21">
         <v>7</v>
       </c>
-      <c r="D183" s="70" t="s">
+      <c r="D183" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E183" s="71"/>
-      <c r="F183" s="72"/>
+      <c r="E183" s="74"/>
+      <c r="F183" s="75"/>
     </row>
     <row r="184" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A184" s="42" t="s">
@@ -9635,62 +9635,62 @@
       </c>
     </row>
     <row r="190" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="73" t="s">
+      <c r="A190" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B190" s="74"/>
+      <c r="B190" s="72"/>
       <c r="C190" s="33">
         <f>'Individual Treasure(2014)'!B21</f>
         <v>2837.3166689405625</v>
       </c>
-      <c r="D190" s="75" t="s">
+      <c r="D190" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E190" s="76"/>
+      <c r="E190" s="70"/>
       <c r="F190" s="34">
         <f>SUMPRODUCT(C185:C189,F185:F189)</f>
         <v>2850</v>
       </c>
     </row>
     <row r="191" spans="1:16" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A191" s="79" t="s">
+      <c r="A191" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="B191" s="79"/>
-      <c r="C191" s="79"/>
-      <c r="D191" s="79"/>
-      <c r="E191" s="79"/>
-      <c r="F191" s="79"/>
-      <c r="G191" s="79"/>
-      <c r="H191" s="79"/>
-      <c r="I191" s="79"/>
-      <c r="J191" s="79"/>
-      <c r="K191" s="79"/>
-      <c r="L191" s="79"/>
+      <c r="B191" s="68"/>
+      <c r="C191" s="68"/>
+      <c r="D191" s="68"/>
+      <c r="E191" s="68"/>
+      <c r="F191" s="68"/>
+      <c r="G191" s="68"/>
+      <c r="H191" s="68"/>
+      <c r="I191" s="68"/>
+      <c r="J191" s="68"/>
+      <c r="K191" s="68"/>
+      <c r="L191" s="68"/>
     </row>
     <row r="192" spans="1:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A192" s="77" t="s">
+      <c r="A192" s="78" t="s">
         <v>89</v>
       </c>
-      <c r="B192" s="77"/>
-      <c r="C192" s="77"/>
-      <c r="D192" s="77"/>
-      <c r="E192" s="77"/>
-      <c r="F192" s="78"/>
+      <c r="B192" s="78"/>
+      <c r="C192" s="78"/>
+      <c r="D192" s="78"/>
+      <c r="E192" s="78"/>
+      <c r="F192" s="79"/>
     </row>
     <row r="193" spans="1:18" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A193" s="68" t="s">
+      <c r="A193" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B193" s="69"/>
+      <c r="B193" s="77"/>
       <c r="C193" s="21">
         <v>7</v>
       </c>
-      <c r="D193" s="70" t="s">
+      <c r="D193" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E193" s="71"/>
-      <c r="F193" s="72"/>
+      <c r="E193" s="74"/>
+      <c r="F193" s="75"/>
     </row>
     <row r="194" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A194" s="42" t="s">
@@ -9829,102 +9829,102 @@
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A200" s="73" t="s">
+      <c r="A200" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B200" s="74"/>
+      <c r="B200" s="72"/>
       <c r="C200" s="33">
         <f>'Individual Treasure(2014)'!B22</f>
         <v>4394.3286689596089</v>
       </c>
-      <c r="D200" s="75" t="s">
+      <c r="D200" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E200" s="76"/>
+      <c r="E200" s="70"/>
       <c r="F200" s="34">
         <f>SUMPRODUCT(C195:C199,F195:F199)</f>
         <v>4075</v>
       </c>
     </row>
     <row r="201" spans="1:18" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A201" s="79" t="s">
+      <c r="A201" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="B201" s="79"/>
-      <c r="C201" s="79"/>
-      <c r="D201" s="79"/>
-      <c r="E201" s="79"/>
-      <c r="F201" s="79"/>
-      <c r="G201" s="79"/>
-      <c r="H201" s="79"/>
-      <c r="I201" s="79"/>
-      <c r="J201" s="79"/>
-      <c r="K201" s="79"/>
-      <c r="L201" s="79"/>
+      <c r="B201" s="68"/>
+      <c r="C201" s="68"/>
+      <c r="D201" s="68"/>
+      <c r="E201" s="68"/>
+      <c r="F201" s="68"/>
+      <c r="G201" s="68"/>
+      <c r="H201" s="68"/>
+      <c r="I201" s="68"/>
+      <c r="J201" s="68"/>
+      <c r="K201" s="68"/>
+      <c r="L201" s="68"/>
     </row>
     <row r="202" spans="1:18" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A202" s="77" t="s">
+      <c r="A202" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="B202" s="77"/>
-      <c r="C202" s="77"/>
-      <c r="D202" s="77"/>
-      <c r="E202" s="77"/>
-      <c r="F202" s="78"/>
-      <c r="G202" s="77" t="s">
+      <c r="B202" s="78"/>
+      <c r="C202" s="78"/>
+      <c r="D202" s="78"/>
+      <c r="E202" s="78"/>
+      <c r="F202" s="79"/>
+      <c r="G202" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="H202" s="77"/>
-      <c r="I202" s="77"/>
-      <c r="J202" s="77"/>
-      <c r="K202" s="77"/>
-      <c r="L202" s="78"/>
-      <c r="M202" s="77" t="s">
+      <c r="H202" s="78"/>
+      <c r="I202" s="78"/>
+      <c r="J202" s="78"/>
+      <c r="K202" s="78"/>
+      <c r="L202" s="79"/>
+      <c r="M202" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="N202" s="77"/>
-      <c r="O202" s="77"/>
-      <c r="P202" s="77"/>
-      <c r="Q202" s="77"/>
-      <c r="R202" s="78"/>
+      <c r="N202" s="78"/>
+      <c r="O202" s="78"/>
+      <c r="P202" s="78"/>
+      <c r="Q202" s="78"/>
+      <c r="R202" s="79"/>
     </row>
     <row r="203" spans="1:18" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A203" s="68" t="s">
+      <c r="A203" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B203" s="69"/>
+      <c r="B203" s="77"/>
       <c r="C203" s="21">
         <v>7</v>
       </c>
-      <c r="D203" s="70" t="s">
+      <c r="D203" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E203" s="71"/>
-      <c r="F203" s="72"/>
-      <c r="G203" s="68" t="s">
+      <c r="E203" s="74"/>
+      <c r="F203" s="75"/>
+      <c r="G203" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H203" s="69"/>
+      <c r="H203" s="77"/>
       <c r="I203" s="21">
         <v>7</v>
       </c>
-      <c r="J203" s="70" t="s">
+      <c r="J203" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K203" s="71"/>
-      <c r="L203" s="72"/>
-      <c r="M203" s="68" t="s">
+      <c r="K203" s="74"/>
+      <c r="L203" s="75"/>
+      <c r="M203" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="N203" s="69"/>
+      <c r="N203" s="77"/>
       <c r="O203" s="21">
         <v>7</v>
       </c>
-      <c r="P203" s="70" t="s">
+      <c r="P203" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="Q203" s="71"/>
-      <c r="R203" s="72"/>
+      <c r="Q203" s="74"/>
+      <c r="R203" s="75"/>
     </row>
     <row r="204" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A204" s="42" t="s">
@@ -10311,50 +10311,50 @@
       </c>
     </row>
     <row r="210" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A210" s="73" t="s">
+      <c r="A210" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B210" s="74"/>
+      <c r="B210" s="72"/>
       <c r="C210" s="33">
         <f>'Individual Treasure(2014)'!B23</f>
         <v>6805.7699241764976</v>
       </c>
-      <c r="D210" s="75" t="s">
+      <c r="D210" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E210" s="76"/>
+      <c r="E210" s="70"/>
       <c r="F210" s="34">
         <f>SUMPRODUCT(C205:C209,F205:F209)</f>
         <v>5700</v>
       </c>
-      <c r="G210" s="73" t="s">
+      <c r="G210" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H210" s="74"/>
+      <c r="H210" s="72"/>
       <c r="I210" s="33">
         <f>'Individual Treasure(2014)'!B23</f>
         <v>6805.7699241764976</v>
       </c>
-      <c r="J210" s="75" t="s">
+      <c r="J210" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K210" s="76"/>
+      <c r="K210" s="70"/>
       <c r="L210" s="34">
         <f>SUMPRODUCT(I205:I209,L205:L209)</f>
         <v>2800</v>
       </c>
-      <c r="M210" s="73" t="s">
+      <c r="M210" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="N210" s="74"/>
+      <c r="N210" s="72"/>
       <c r="O210" s="33">
         <f>'Individual Treasure(2014)'!B23</f>
         <v>6805.7699241764976</v>
       </c>
-      <c r="P210" s="75" t="s">
+      <c r="P210" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="Q210" s="76"/>
+      <c r="Q210" s="70"/>
       <c r="R210" s="34">
         <f>SUMPRODUCT(O205:O209,R205:R209)</f>
         <v>5000</v>
@@ -10365,84 +10365,84 @@
       </c>
     </row>
     <row r="211" spans="1:19" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A211" s="79" t="s">
+      <c r="A211" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="B211" s="79"/>
-      <c r="C211" s="79"/>
-      <c r="D211" s="79"/>
-      <c r="E211" s="79"/>
-      <c r="F211" s="79"/>
-      <c r="G211" s="79"/>
-      <c r="H211" s="79"/>
-      <c r="I211" s="79"/>
-      <c r="J211" s="79"/>
-      <c r="K211" s="79"/>
-      <c r="L211" s="79"/>
+      <c r="B211" s="68"/>
+      <c r="C211" s="68"/>
+      <c r="D211" s="68"/>
+      <c r="E211" s="68"/>
+      <c r="F211" s="68"/>
+      <c r="G211" s="68"/>
+      <c r="H211" s="68"/>
+      <c r="I211" s="68"/>
+      <c r="J211" s="68"/>
+      <c r="K211" s="68"/>
+      <c r="L211" s="68"/>
     </row>
     <row r="212" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A212" s="77" t="s">
+      <c r="A212" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="B212" s="77"/>
-      <c r="C212" s="77"/>
-      <c r="D212" s="77"/>
-      <c r="E212" s="77"/>
-      <c r="F212" s="78"/>
-      <c r="G212" s="77" t="s">
+      <c r="B212" s="78"/>
+      <c r="C212" s="78"/>
+      <c r="D212" s="78"/>
+      <c r="E212" s="78"/>
+      <c r="F212" s="79"/>
+      <c r="G212" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="H212" s="77"/>
-      <c r="I212" s="77"/>
-      <c r="J212" s="77"/>
-      <c r="K212" s="77"/>
-      <c r="L212" s="78"/>
-      <c r="M212" s="77" t="s">
+      <c r="H212" s="78"/>
+      <c r="I212" s="78"/>
+      <c r="J212" s="78"/>
+      <c r="K212" s="78"/>
+      <c r="L212" s="79"/>
+      <c r="M212" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="N212" s="77"/>
-      <c r="O212" s="77"/>
-      <c r="P212" s="77"/>
-      <c r="Q212" s="77"/>
-      <c r="R212" s="78"/>
+      <c r="N212" s="78"/>
+      <c r="O212" s="78"/>
+      <c r="P212" s="78"/>
+      <c r="Q212" s="78"/>
+      <c r="R212" s="79"/>
     </row>
     <row r="213" spans="1:19" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A213" s="68" t="s">
+      <c r="A213" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B213" s="69"/>
+      <c r="B213" s="77"/>
       <c r="C213" s="21">
         <v>7</v>
       </c>
-      <c r="D213" s="70" t="s">
+      <c r="D213" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E213" s="71"/>
-      <c r="F213" s="72"/>
-      <c r="G213" s="68" t="s">
+      <c r="E213" s="74"/>
+      <c r="F213" s="75"/>
+      <c r="G213" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H213" s="69"/>
+      <c r="H213" s="77"/>
       <c r="I213" s="21">
         <v>7</v>
       </c>
-      <c r="J213" s="70" t="s">
+      <c r="J213" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K213" s="71"/>
-      <c r="L213" s="72"/>
-      <c r="M213" s="68" t="s">
+      <c r="K213" s="74"/>
+      <c r="L213" s="75"/>
+      <c r="M213" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="N213" s="69"/>
+      <c r="N213" s="77"/>
       <c r="O213" s="21">
         <v>7</v>
       </c>
-      <c r="P213" s="70" t="s">
+      <c r="P213" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="Q213" s="71"/>
-      <c r="R213" s="72"/>
+      <c r="Q213" s="74"/>
+      <c r="R213" s="75"/>
     </row>
     <row r="214" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A214" s="42" t="s">
@@ -10829,50 +10829,50 @@
       </c>
     </row>
     <row r="220" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A220" s="73" t="s">
+      <c r="A220" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B220" s="74"/>
+      <c r="B220" s="72"/>
       <c r="C220" s="33">
         <f>'Individual Treasure(2014)'!B24</f>
         <v>10540.518871063789</v>
       </c>
-      <c r="D220" s="75" t="s">
+      <c r="D220" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E220" s="76"/>
+      <c r="E220" s="70"/>
       <c r="F220" s="34">
         <f>SUMPRODUCT(C215:C219,F215:F219)</f>
         <v>8400</v>
       </c>
-      <c r="G220" s="73" t="s">
+      <c r="G220" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H220" s="74"/>
+      <c r="H220" s="72"/>
       <c r="I220" s="33">
         <f>'Individual Treasure(2014)'!B24</f>
         <v>10540.518871063789</v>
       </c>
-      <c r="J220" s="75" t="s">
+      <c r="J220" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K220" s="76"/>
+      <c r="K220" s="70"/>
       <c r="L220" s="34">
         <f>SUMPRODUCT(I215:I219,L215:L219)</f>
         <v>5450</v>
       </c>
-      <c r="M220" s="73" t="s">
+      <c r="M220" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="N220" s="74"/>
+      <c r="N220" s="72"/>
       <c r="O220" s="33">
         <f>'Individual Treasure(2014)'!B24</f>
         <v>10540.518871063789</v>
       </c>
-      <c r="P220" s="75" t="s">
+      <c r="P220" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="Q220" s="76"/>
+      <c r="Q220" s="70"/>
       <c r="R220" s="34">
         <f>SUMPRODUCT(O215:O219,R215:R219)</f>
         <v>2300</v>
@@ -10883,64 +10883,64 @@
       </c>
     </row>
     <row r="221" spans="1:19" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A221" s="79" t="s">
+      <c r="A221" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="B221" s="79"/>
-      <c r="C221" s="79"/>
-      <c r="D221" s="79"/>
-      <c r="E221" s="79"/>
-      <c r="F221" s="79"/>
-      <c r="G221" s="79"/>
-      <c r="H221" s="79"/>
-      <c r="I221" s="79"/>
-      <c r="J221" s="79"/>
-      <c r="K221" s="79"/>
-      <c r="L221" s="79"/>
+      <c r="B221" s="68"/>
+      <c r="C221" s="68"/>
+      <c r="D221" s="68"/>
+      <c r="E221" s="68"/>
+      <c r="F221" s="68"/>
+      <c r="G221" s="68"/>
+      <c r="H221" s="68"/>
+      <c r="I221" s="68"/>
+      <c r="J221" s="68"/>
+      <c r="K221" s="68"/>
+      <c r="L221" s="68"/>
     </row>
     <row r="222" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A222" s="77" t="s">
+      <c r="A222" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="B222" s="77"/>
-      <c r="C222" s="77"/>
-      <c r="D222" s="77"/>
-      <c r="E222" s="77"/>
-      <c r="F222" s="78"/>
-      <c r="G222" s="77" t="s">
+      <c r="B222" s="78"/>
+      <c r="C222" s="78"/>
+      <c r="D222" s="78"/>
+      <c r="E222" s="78"/>
+      <c r="F222" s="79"/>
+      <c r="G222" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="H222" s="77"/>
-      <c r="I222" s="77"/>
-      <c r="J222" s="77"/>
-      <c r="K222" s="77"/>
-      <c r="L222" s="78"/>
+      <c r="H222" s="78"/>
+      <c r="I222" s="78"/>
+      <c r="J222" s="78"/>
+      <c r="K222" s="78"/>
+      <c r="L222" s="79"/>
     </row>
     <row r="223" spans="1:19" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A223" s="68" t="s">
+      <c r="A223" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B223" s="69"/>
+      <c r="B223" s="77"/>
       <c r="C223" s="21">
         <v>7</v>
       </c>
-      <c r="D223" s="70" t="s">
+      <c r="D223" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E223" s="71"/>
-      <c r="F223" s="72"/>
-      <c r="G223" s="68" t="s">
+      <c r="E223" s="74"/>
+      <c r="F223" s="75"/>
+      <c r="G223" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H223" s="69"/>
+      <c r="H223" s="77"/>
       <c r="I223" s="21">
         <v>7</v>
       </c>
-      <c r="J223" s="70" t="s">
+      <c r="J223" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K223" s="71"/>
-      <c r="L223" s="72"/>
+      <c r="K223" s="74"/>
+      <c r="L223" s="75"/>
     </row>
     <row r="224" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A224" s="42" t="s">
@@ -11203,98 +11203,98 @@
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A230" s="73" t="s">
+      <c r="A230" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B230" s="74"/>
+      <c r="B230" s="72"/>
       <c r="C230" s="33">
         <f>'Individual Treasure(2014)'!B25</f>
         <v>16324.756685731661</v>
       </c>
-      <c r="D230" s="75" t="s">
+      <c r="D230" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E230" s="76"/>
+      <c r="E230" s="70"/>
       <c r="F230" s="34">
         <f>SUMPRODUCT(C225:C229,F225:F229)</f>
         <v>16900</v>
       </c>
-      <c r="G230" s="73" t="s">
+      <c r="G230" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H230" s="74"/>
+      <c r="H230" s="72"/>
       <c r="I230" s="33">
         <f>'Individual Treasure(2014)'!B15</f>
         <v>205.58879840633722</v>
       </c>
-      <c r="J230" s="75" t="s">
+      <c r="J230" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K230" s="76"/>
+      <c r="K230" s="70"/>
       <c r="L230" s="34">
         <f>SUMPRODUCT(I225:I229,L225:L229)</f>
         <v>17250</v>
       </c>
     </row>
     <row r="231" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A231" s="79" t="s">
+      <c r="A231" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="B231" s="79"/>
-      <c r="C231" s="79"/>
-      <c r="D231" s="79"/>
-      <c r="E231" s="79"/>
-      <c r="F231" s="79"/>
-      <c r="G231" s="79"/>
-      <c r="H231" s="79"/>
-      <c r="I231" s="79"/>
-      <c r="J231" s="79"/>
-      <c r="K231" s="79"/>
-      <c r="L231" s="79"/>
+      <c r="B231" s="68"/>
+      <c r="C231" s="68"/>
+      <c r="D231" s="68"/>
+      <c r="E231" s="68"/>
+      <c r="F231" s="68"/>
+      <c r="G231" s="68"/>
+      <c r="H231" s="68"/>
+      <c r="I231" s="68"/>
+      <c r="J231" s="68"/>
+      <c r="K231" s="68"/>
+      <c r="L231" s="68"/>
     </row>
     <row r="232" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A232" s="77" t="s">
+      <c r="A232" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="B232" s="77"/>
-      <c r="C232" s="77"/>
-      <c r="D232" s="77"/>
-      <c r="E232" s="77"/>
-      <c r="F232" s="78"/>
-      <c r="G232" s="77" t="s">
+      <c r="B232" s="78"/>
+      <c r="C232" s="78"/>
+      <c r="D232" s="78"/>
+      <c r="E232" s="78"/>
+      <c r="F232" s="79"/>
+      <c r="G232" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="H232" s="77"/>
-      <c r="I232" s="77"/>
-      <c r="J232" s="77"/>
-      <c r="K232" s="77"/>
-      <c r="L232" s="78"/>
+      <c r="H232" s="78"/>
+      <c r="I232" s="78"/>
+      <c r="J232" s="78"/>
+      <c r="K232" s="78"/>
+      <c r="L232" s="79"/>
     </row>
     <row r="233" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A233" s="68" t="s">
+      <c r="A233" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B233" s="69"/>
+      <c r="B233" s="77"/>
       <c r="C233" s="21">
         <v>7</v>
       </c>
-      <c r="D233" s="70" t="s">
+      <c r="D233" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E233" s="71"/>
-      <c r="F233" s="72"/>
-      <c r="G233" s="68" t="s">
+      <c r="E233" s="74"/>
+      <c r="F233" s="75"/>
+      <c r="G233" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H233" s="69"/>
+      <c r="H233" s="77"/>
       <c r="I233" s="21">
         <v>7</v>
       </c>
-      <c r="J233" s="70" t="s">
+      <c r="J233" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K233" s="71"/>
-      <c r="L233" s="72"/>
+      <c r="K233" s="74"/>
+      <c r="L233" s="75"/>
     </row>
     <row r="234" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A234" s="42" t="s">
@@ -11557,78 +11557,78 @@
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A240" s="73" t="s">
+      <c r="A240" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B240" s="74"/>
+      <c r="B240" s="72"/>
       <c r="C240" s="33">
         <f>'Individual Treasure(2014)'!B26</f>
         <v>25283.165288944179</v>
       </c>
-      <c r="D240" s="75" t="s">
+      <c r="D240" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E240" s="76"/>
+      <c r="E240" s="70"/>
       <c r="F240" s="34">
         <f>SUMPRODUCT(C235:C239,F235:F239)</f>
         <v>17100</v>
       </c>
-      <c r="G240" s="73" t="s">
+      <c r="G240" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H240" s="74"/>
+      <c r="H240" s="72"/>
       <c r="I240" s="33">
         <f>'Individual Treasure(2014)'!B25</f>
         <v>16324.756685731661</v>
       </c>
-      <c r="J240" s="75" t="s">
+      <c r="J240" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K240" s="76"/>
+      <c r="K240" s="70"/>
       <c r="L240" s="34">
         <f>SUMPRODUCT(I235:I239,L235:L239)</f>
         <v>17250</v>
       </c>
     </row>
     <row r="241" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A241" s="79" t="s">
+      <c r="A241" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="B241" s="79"/>
-      <c r="C241" s="79"/>
-      <c r="D241" s="79"/>
-      <c r="E241" s="79"/>
-      <c r="F241" s="79"/>
-      <c r="G241" s="79"/>
-      <c r="H241" s="79"/>
-      <c r="I241" s="79"/>
-      <c r="J241" s="79"/>
-      <c r="K241" s="79"/>
-      <c r="L241" s="79"/>
+      <c r="B241" s="68"/>
+      <c r="C241" s="68"/>
+      <c r="D241" s="68"/>
+      <c r="E241" s="68"/>
+      <c r="F241" s="68"/>
+      <c r="G241" s="68"/>
+      <c r="H241" s="68"/>
+      <c r="I241" s="68"/>
+      <c r="J241" s="68"/>
+      <c r="K241" s="68"/>
+      <c r="L241" s="68"/>
     </row>
     <row r="242" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A242" s="77" t="s">
+      <c r="A242" s="78" t="s">
         <v>93</v>
       </c>
-      <c r="B242" s="77"/>
-      <c r="C242" s="77"/>
-      <c r="D242" s="77"/>
-      <c r="E242" s="77"/>
-      <c r="F242" s="78"/>
+      <c r="B242" s="78"/>
+      <c r="C242" s="78"/>
+      <c r="D242" s="78"/>
+      <c r="E242" s="78"/>
+      <c r="F242" s="79"/>
     </row>
     <row r="243" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A243" s="68" t="s">
+      <c r="A243" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B243" s="69"/>
+      <c r="B243" s="77"/>
       <c r="C243" s="21">
         <v>7</v>
       </c>
-      <c r="D243" s="70" t="s">
+      <c r="D243" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E243" s="71"/>
-      <c r="F243" s="72"/>
+      <c r="E243" s="74"/>
+      <c r="F243" s="75"/>
     </row>
     <row r="244" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A244" s="42" t="s">
@@ -11767,62 +11767,62 @@
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A250" s="73" t="s">
+      <c r="A250" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B250" s="74"/>
+      <c r="B250" s="72"/>
       <c r="C250" s="33">
         <f>'Individual Treasure(2014)'!B27</f>
         <v>39157.609472169628</v>
       </c>
-      <c r="D250" s="75" t="s">
+      <c r="D250" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E250" s="76"/>
+      <c r="E250" s="70"/>
       <c r="F250" s="34">
         <f>SUMPRODUCT(C245:C249,F245:F249)</f>
         <v>28000</v>
       </c>
     </row>
     <row r="251" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A251" s="79" t="s">
+      <c r="A251" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="B251" s="79"/>
-      <c r="C251" s="79"/>
-      <c r="D251" s="79"/>
-      <c r="E251" s="79"/>
-      <c r="F251" s="79"/>
-      <c r="G251" s="79"/>
-      <c r="H251" s="79"/>
-      <c r="I251" s="79"/>
-      <c r="J251" s="79"/>
-      <c r="K251" s="79"/>
-      <c r="L251" s="79"/>
+      <c r="B251" s="68"/>
+      <c r="C251" s="68"/>
+      <c r="D251" s="68"/>
+      <c r="E251" s="68"/>
+      <c r="F251" s="68"/>
+      <c r="G251" s="68"/>
+      <c r="H251" s="68"/>
+      <c r="I251" s="68"/>
+      <c r="J251" s="68"/>
+      <c r="K251" s="68"/>
+      <c r="L251" s="68"/>
     </row>
     <row r="252" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A252" s="77" t="s">
+      <c r="A252" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="B252" s="77"/>
-      <c r="C252" s="77"/>
-      <c r="D252" s="77"/>
-      <c r="E252" s="77"/>
-      <c r="F252" s="78"/>
+      <c r="B252" s="78"/>
+      <c r="C252" s="78"/>
+      <c r="D252" s="78"/>
+      <c r="E252" s="78"/>
+      <c r="F252" s="79"/>
     </row>
     <row r="253" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A253" s="68" t="s">
+      <c r="A253" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B253" s="69"/>
+      <c r="B253" s="77"/>
       <c r="C253" s="21">
         <v>7</v>
       </c>
-      <c r="D253" s="70" t="s">
+      <c r="D253" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E253" s="71"/>
-      <c r="F253" s="72"/>
+      <c r="E253" s="74"/>
+      <c r="F253" s="75"/>
     </row>
     <row r="254" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A254" s="42" t="s">
@@ -11961,102 +11961,102 @@
       </c>
     </row>
     <row r="260" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A260" s="73" t="s">
+      <c r="A260" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B260" s="74"/>
+      <c r="B260" s="72"/>
       <c r="C260" s="33">
         <f>'Individual Treasure(2014)'!B28</f>
         <v>60645.823497639387</v>
       </c>
-      <c r="D260" s="75" t="s">
+      <c r="D260" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E260" s="76"/>
+      <c r="E260" s="70"/>
       <c r="F260" s="34">
         <f>SUMPRODUCT(C255:C259,F255:F259)</f>
         <v>41000</v>
       </c>
     </row>
     <row r="261" spans="1:19" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A261" s="79" t="s">
+      <c r="A261" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="B261" s="79"/>
-      <c r="C261" s="79"/>
-      <c r="D261" s="79"/>
-      <c r="E261" s="79"/>
-      <c r="F261" s="79"/>
-      <c r="G261" s="79"/>
-      <c r="H261" s="79"/>
-      <c r="I261" s="79"/>
-      <c r="J261" s="79"/>
-      <c r="K261" s="79"/>
-      <c r="L261" s="79"/>
+      <c r="B261" s="68"/>
+      <c r="C261" s="68"/>
+      <c r="D261" s="68"/>
+      <c r="E261" s="68"/>
+      <c r="F261" s="68"/>
+      <c r="G261" s="68"/>
+      <c r="H261" s="68"/>
+      <c r="I261" s="68"/>
+      <c r="J261" s="68"/>
+      <c r="K261" s="68"/>
+      <c r="L261" s="68"/>
     </row>
     <row r="262" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A262" s="77" t="s">
+      <c r="A262" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B262" s="77"/>
-      <c r="C262" s="77"/>
-      <c r="D262" s="77"/>
-      <c r="E262" s="77"/>
-      <c r="F262" s="78"/>
-      <c r="G262" s="77" t="s">
+      <c r="B262" s="78"/>
+      <c r="C262" s="78"/>
+      <c r="D262" s="78"/>
+      <c r="E262" s="78"/>
+      <c r="F262" s="79"/>
+      <c r="G262" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="H262" s="77"/>
-      <c r="I262" s="77"/>
-      <c r="J262" s="77"/>
-      <c r="K262" s="77"/>
-      <c r="L262" s="78"/>
-      <c r="M262" s="77" t="s">
+      <c r="H262" s="78"/>
+      <c r="I262" s="78"/>
+      <c r="J262" s="78"/>
+      <c r="K262" s="78"/>
+      <c r="L262" s="79"/>
+      <c r="M262" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="N262" s="77"/>
-      <c r="O262" s="77"/>
-      <c r="P262" s="77"/>
-      <c r="Q262" s="77"/>
-      <c r="R262" s="78"/>
+      <c r="N262" s="78"/>
+      <c r="O262" s="78"/>
+      <c r="P262" s="78"/>
+      <c r="Q262" s="78"/>
+      <c r="R262" s="79"/>
     </row>
     <row r="263" spans="1:19" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A263" s="68" t="s">
+      <c r="A263" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B263" s="69"/>
+      <c r="B263" s="77"/>
       <c r="C263" s="21">
         <v>7</v>
       </c>
-      <c r="D263" s="70" t="s">
+      <c r="D263" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E263" s="71"/>
-      <c r="F263" s="72"/>
-      <c r="G263" s="68" t="s">
+      <c r="E263" s="74"/>
+      <c r="F263" s="75"/>
+      <c r="G263" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H263" s="69"/>
+      <c r="H263" s="77"/>
       <c r="I263" s="21">
         <v>7</v>
       </c>
-      <c r="J263" s="70" t="s">
+      <c r="J263" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K263" s="71"/>
-      <c r="L263" s="72"/>
-      <c r="M263" s="68" t="s">
+      <c r="K263" s="74"/>
+      <c r="L263" s="75"/>
+      <c r="M263" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="N263" s="69"/>
+      <c r="N263" s="77"/>
       <c r="O263" s="21">
         <v>7</v>
       </c>
-      <c r="P263" s="70" t="s">
+      <c r="P263" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="Q263" s="71"/>
-      <c r="R263" s="72"/>
+      <c r="Q263" s="74"/>
+      <c r="R263" s="75"/>
     </row>
     <row r="264" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A264" s="42" t="s">
@@ -12443,50 +12443,50 @@
       </c>
     </row>
     <row r="270" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A270" s="73" t="s">
+      <c r="A270" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B270" s="74"/>
+      <c r="B270" s="72"/>
       <c r="C270" s="33">
         <f>'Individual Treasure(2014)'!B29</f>
         <v>93925.956085772239</v>
       </c>
-      <c r="D270" s="75" t="s">
+      <c r="D270" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E270" s="76"/>
+      <c r="E270" s="70"/>
       <c r="F270" s="34">
         <f>SUMPRODUCT(C265:C269,F265:F269)</f>
         <v>205000</v>
       </c>
-      <c r="G270" s="73" t="s">
+      <c r="G270" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H270" s="74"/>
+      <c r="H270" s="72"/>
       <c r="I270" s="33">
         <f>'Individual Treasure(2014)'!B29</f>
         <v>93925.956085772239</v>
       </c>
-      <c r="J270" s="75" t="s">
+      <c r="J270" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K270" s="76"/>
+      <c r="K270" s="70"/>
       <c r="L270" s="34">
         <f>SUMPRODUCT(I265:I269,L265:L269)</f>
         <v>31500.000000000004</v>
       </c>
-      <c r="M270" s="73" t="s">
+      <c r="M270" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="N270" s="74"/>
+      <c r="N270" s="72"/>
       <c r="O270" s="33">
         <f>'Individual Treasure(2014)'!B29</f>
         <v>93925.956085772239</v>
       </c>
-      <c r="P270" s="75" t="s">
+      <c r="P270" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="Q270" s="76"/>
+      <c r="Q270" s="70"/>
       <c r="R270" s="34">
         <f>SUMPRODUCT(O265:O269,R265:R269)</f>
         <v>67500</v>
@@ -12497,64 +12497,64 @@
       </c>
     </row>
     <row r="271" spans="1:19" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A271" s="79" t="s">
+      <c r="A271" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="B271" s="79"/>
-      <c r="C271" s="79"/>
-      <c r="D271" s="79"/>
-      <c r="E271" s="79"/>
-      <c r="F271" s="79"/>
-      <c r="G271" s="79"/>
-      <c r="H271" s="79"/>
-      <c r="I271" s="79"/>
-      <c r="J271" s="79"/>
-      <c r="K271" s="79"/>
-      <c r="L271" s="79"/>
+      <c r="B271" s="68"/>
+      <c r="C271" s="68"/>
+      <c r="D271" s="68"/>
+      <c r="E271" s="68"/>
+      <c r="F271" s="68"/>
+      <c r="G271" s="68"/>
+      <c r="H271" s="68"/>
+      <c r="I271" s="68"/>
+      <c r="J271" s="68"/>
+      <c r="K271" s="68"/>
+      <c r="L271" s="68"/>
     </row>
     <row r="272" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A272" s="77" t="s">
+      <c r="A272" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="B272" s="77"/>
-      <c r="C272" s="77"/>
-      <c r="D272" s="77"/>
-      <c r="E272" s="77"/>
-      <c r="F272" s="78"/>
-      <c r="G272" s="77" t="s">
+      <c r="B272" s="78"/>
+      <c r="C272" s="78"/>
+      <c r="D272" s="78"/>
+      <c r="E272" s="78"/>
+      <c r="F272" s="79"/>
+      <c r="G272" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="H272" s="77"/>
-      <c r="I272" s="77"/>
-      <c r="J272" s="77"/>
-      <c r="K272" s="77"/>
-      <c r="L272" s="78"/>
+      <c r="H272" s="78"/>
+      <c r="I272" s="78"/>
+      <c r="J272" s="78"/>
+      <c r="K272" s="78"/>
+      <c r="L272" s="79"/>
     </row>
     <row r="273" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A273" s="68" t="s">
+      <c r="A273" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B273" s="69"/>
+      <c r="B273" s="77"/>
       <c r="C273" s="21">
         <v>7</v>
       </c>
-      <c r="D273" s="70" t="s">
+      <c r="D273" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E273" s="71"/>
-      <c r="F273" s="72"/>
-      <c r="G273" s="68" t="s">
+      <c r="E273" s="74"/>
+      <c r="F273" s="75"/>
+      <c r="G273" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H273" s="69"/>
+      <c r="H273" s="77"/>
       <c r="I273" s="21">
         <v>7</v>
       </c>
-      <c r="J273" s="70" t="s">
+      <c r="J273" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K273" s="71"/>
-      <c r="L273" s="72"/>
+      <c r="K273" s="74"/>
+      <c r="L273" s="75"/>
     </row>
     <row r="274" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A274" s="42" t="s">
@@ -12817,98 +12817,98 @@
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A280" s="73" t="s">
+      <c r="A280" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B280" s="74"/>
+      <c r="B280" s="72"/>
       <c r="C280" s="33">
         <f>'Individual Treasure(2014)'!B30</f>
         <v>145468.96583851028</v>
       </c>
-      <c r="D280" s="75" t="s">
+      <c r="D280" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E280" s="76"/>
+      <c r="E280" s="70"/>
       <c r="F280" s="34">
         <f>SUMPRODUCT(C275:C279,F275:F279)</f>
         <v>81500</v>
       </c>
-      <c r="G280" s="73" t="s">
+      <c r="G280" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H280" s="74"/>
+      <c r="H280" s="72"/>
       <c r="I280" s="33">
         <f>'Individual Treasure(2014)'!B39</f>
         <v>0</v>
       </c>
-      <c r="J280" s="75" t="s">
+      <c r="J280" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K280" s="76"/>
+      <c r="K280" s="70"/>
       <c r="L280" s="34">
         <f>SUMPRODUCT(I275:I279,L275:L279)</f>
         <v>31500.000000000004</v>
       </c>
     </row>
     <row r="281" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A281" s="79" t="s">
+      <c r="A281" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="B281" s="79"/>
-      <c r="C281" s="79"/>
-      <c r="D281" s="79"/>
-      <c r="E281" s="79"/>
-      <c r="F281" s="79"/>
-      <c r="G281" s="79"/>
-      <c r="H281" s="79"/>
-      <c r="I281" s="79"/>
-      <c r="J281" s="79"/>
-      <c r="K281" s="79"/>
-      <c r="L281" s="79"/>
+      <c r="B281" s="68"/>
+      <c r="C281" s="68"/>
+      <c r="D281" s="68"/>
+      <c r="E281" s="68"/>
+      <c r="F281" s="68"/>
+      <c r="G281" s="68"/>
+      <c r="H281" s="68"/>
+      <c r="I281" s="68"/>
+      <c r="J281" s="68"/>
+      <c r="K281" s="68"/>
+      <c r="L281" s="68"/>
     </row>
     <row r="282" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A282" s="77" t="s">
+      <c r="A282" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="B282" s="77"/>
-      <c r="C282" s="77"/>
-      <c r="D282" s="77"/>
-      <c r="E282" s="77"/>
-      <c r="F282" s="78"/>
-      <c r="G282" s="77" t="s">
+      <c r="B282" s="78"/>
+      <c r="C282" s="78"/>
+      <c r="D282" s="78"/>
+      <c r="E282" s="78"/>
+      <c r="F282" s="79"/>
+      <c r="G282" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="H282" s="77"/>
-      <c r="I282" s="77"/>
-      <c r="J282" s="77"/>
-      <c r="K282" s="77"/>
-      <c r="L282" s="78"/>
+      <c r="H282" s="78"/>
+      <c r="I282" s="78"/>
+      <c r="J282" s="78"/>
+      <c r="K282" s="78"/>
+      <c r="L282" s="79"/>
     </row>
     <row r="283" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A283" s="68" t="s">
+      <c r="A283" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B283" s="69"/>
+      <c r="B283" s="77"/>
       <c r="C283" s="21">
         <v>7</v>
       </c>
-      <c r="D283" s="70" t="s">
+      <c r="D283" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E283" s="71"/>
-      <c r="F283" s="72"/>
-      <c r="G283" s="68" t="s">
+      <c r="E283" s="74"/>
+      <c r="F283" s="75"/>
+      <c r="G283" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H283" s="69"/>
+      <c r="H283" s="77"/>
       <c r="I283" s="21">
         <v>7</v>
       </c>
-      <c r="J283" s="70" t="s">
+      <c r="J283" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K283" s="71"/>
-      <c r="L283" s="72"/>
+      <c r="K283" s="74"/>
+      <c r="L283" s="75"/>
     </row>
     <row r="284" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A284" s="42" t="s">
@@ -13171,98 +13171,98 @@
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A290" s="73" t="s">
+      <c r="A290" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B290" s="74"/>
+      <c r="B290" s="72"/>
       <c r="C290" s="33">
         <f>'Individual Treasure(2014)'!B31</f>
         <v>225296.82852311266</v>
       </c>
-      <c r="D290" s="75" t="s">
+      <c r="D290" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E290" s="76"/>
+      <c r="E290" s="70"/>
       <c r="F290" s="34">
         <f>SUMPRODUCT(C285:C289,F285:F289)</f>
         <v>130000</v>
       </c>
-      <c r="G290" s="73" t="s">
+      <c r="G290" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H290" s="74"/>
+      <c r="H290" s="72"/>
       <c r="I290" s="33">
         <f>'Individual Treasure(2014)'!B49</f>
         <v>0</v>
       </c>
-      <c r="J290" s="75" t="s">
+      <c r="J290" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K290" s="76"/>
+      <c r="K290" s="70"/>
       <c r="L290" s="34">
         <f>SUMPRODUCT(I285:I289,L285:L289)</f>
         <v>31500.000000000004</v>
       </c>
     </row>
     <row r="291" spans="1:12" ht="28.5" x14ac:dyDescent="0.35">
-      <c r="A291" s="79" t="s">
+      <c r="A291" s="68" t="s">
         <v>113</v>
       </c>
-      <c r="B291" s="79"/>
-      <c r="C291" s="79"/>
-      <c r="D291" s="79"/>
-      <c r="E291" s="79"/>
-      <c r="F291" s="79"/>
-      <c r="G291" s="79"/>
-      <c r="H291" s="79"/>
-      <c r="I291" s="79"/>
-      <c r="J291" s="79"/>
-      <c r="K291" s="79"/>
-      <c r="L291" s="79"/>
+      <c r="B291" s="68"/>
+      <c r="C291" s="68"/>
+      <c r="D291" s="68"/>
+      <c r="E291" s="68"/>
+      <c r="F291" s="68"/>
+      <c r="G291" s="68"/>
+      <c r="H291" s="68"/>
+      <c r="I291" s="68"/>
+      <c r="J291" s="68"/>
+      <c r="K291" s="68"/>
+      <c r="L291" s="68"/>
     </row>
     <row r="292" spans="1:12" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A292" s="77" t="s">
+      <c r="A292" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="B292" s="77"/>
-      <c r="C292" s="77"/>
-      <c r="D292" s="77"/>
-      <c r="E292" s="77"/>
-      <c r="F292" s="78"/>
-      <c r="G292" s="77" t="s">
+      <c r="B292" s="78"/>
+      <c r="C292" s="78"/>
+      <c r="D292" s="78"/>
+      <c r="E292" s="78"/>
+      <c r="F292" s="79"/>
+      <c r="G292" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="H292" s="77"/>
-      <c r="I292" s="77"/>
-      <c r="J292" s="77"/>
-      <c r="K292" s="77"/>
-      <c r="L292" s="78"/>
+      <c r="H292" s="78"/>
+      <c r="I292" s="78"/>
+      <c r="J292" s="78"/>
+      <c r="K292" s="78"/>
+      <c r="L292" s="79"/>
     </row>
     <row r="293" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A293" s="68" t="s">
+      <c r="A293" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="B293" s="69"/>
+      <c r="B293" s="77"/>
       <c r="C293" s="21">
         <v>7</v>
       </c>
-      <c r="D293" s="70" t="s">
+      <c r="D293" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E293" s="71"/>
-      <c r="F293" s="72"/>
-      <c r="G293" s="68" t="s">
+      <c r="E293" s="74"/>
+      <c r="F293" s="75"/>
+      <c r="G293" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="H293" s="69"/>
+      <c r="H293" s="77"/>
       <c r="I293" s="21">
         <v>7</v>
       </c>
-      <c r="J293" s="70" t="s">
+      <c r="J293" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="K293" s="71"/>
-      <c r="L293" s="72"/>
+      <c r="K293" s="74"/>
+      <c r="L293" s="75"/>
     </row>
     <row r="294" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A294" s="42" t="s">
@@ -13525,34 +13525,34 @@
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A300" s="73" t="s">
+      <c r="A300" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B300" s="74"/>
+      <c r="B300" s="72"/>
       <c r="C300" s="33">
         <f>'Individual Treasure(2014)'!B41</f>
         <v>0</v>
       </c>
-      <c r="D300" s="75" t="s">
+      <c r="D300" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="E300" s="76"/>
+      <c r="E300" s="70"/>
       <c r="F300" s="34">
         <f>SUMPRODUCT(C295:C299,F295:F299)</f>
         <v>280000</v>
       </c>
-      <c r="G300" s="73" t="s">
+      <c r="G300" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="H300" s="74"/>
+      <c r="H300" s="72"/>
       <c r="I300" s="33">
         <f>'Individual Treasure(2014)'!B59</f>
         <v>0</v>
       </c>
-      <c r="J300" s="75" t="s">
+      <c r="J300" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="K300" s="76"/>
+      <c r="K300" s="70"/>
       <c r="L300" s="34">
         <f>SUMPRODUCT(I295:I299,L295:L299)</f>
         <v>31500.000000000004</v>
@@ -13560,28 +13560,270 @@
     </row>
   </sheetData>
   <mergeCells count="310">
-    <mergeCell ref="A291:L291"/>
-    <mergeCell ref="J300:K300"/>
-    <mergeCell ref="G300:H300"/>
-    <mergeCell ref="D300:E300"/>
-    <mergeCell ref="A300:B300"/>
-    <mergeCell ref="J293:L293"/>
-    <mergeCell ref="G293:H293"/>
-    <mergeCell ref="D293:F293"/>
-    <mergeCell ref="A293:B293"/>
-    <mergeCell ref="G292:L292"/>
-    <mergeCell ref="A292:F292"/>
-    <mergeCell ref="A281:L281"/>
-    <mergeCell ref="A282:F282"/>
-    <mergeCell ref="G282:L282"/>
-    <mergeCell ref="A283:B283"/>
-    <mergeCell ref="D283:F283"/>
-    <mergeCell ref="G283:H283"/>
-    <mergeCell ref="J283:L283"/>
-    <mergeCell ref="A290:B290"/>
-    <mergeCell ref="D290:E290"/>
-    <mergeCell ref="G290:H290"/>
-    <mergeCell ref="J290:K290"/>
+    <mergeCell ref="A213:B213"/>
+    <mergeCell ref="D213:F213"/>
+    <mergeCell ref="G213:H213"/>
+    <mergeCell ref="J213:L213"/>
+    <mergeCell ref="A220:B220"/>
+    <mergeCell ref="D220:E220"/>
+    <mergeCell ref="G220:H220"/>
+    <mergeCell ref="J220:K220"/>
+    <mergeCell ref="G232:L232"/>
+    <mergeCell ref="A221:L221"/>
+    <mergeCell ref="A222:F222"/>
+    <mergeCell ref="G222:L222"/>
+    <mergeCell ref="A223:B223"/>
+    <mergeCell ref="D223:F223"/>
+    <mergeCell ref="G223:H223"/>
+    <mergeCell ref="J223:L223"/>
+    <mergeCell ref="A230:B230"/>
+    <mergeCell ref="D230:E230"/>
+    <mergeCell ref="G230:H230"/>
+    <mergeCell ref="J230:K230"/>
+    <mergeCell ref="G32:L32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="G42:L42"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="A262:F262"/>
+    <mergeCell ref="A263:B263"/>
+    <mergeCell ref="D263:F263"/>
+    <mergeCell ref="A270:B270"/>
+    <mergeCell ref="D270:E270"/>
+    <mergeCell ref="A240:B240"/>
+    <mergeCell ref="D240:E240"/>
+    <mergeCell ref="A241:L241"/>
+    <mergeCell ref="A242:F242"/>
+    <mergeCell ref="A243:B243"/>
+    <mergeCell ref="D243:F243"/>
+    <mergeCell ref="A250:B250"/>
+    <mergeCell ref="D250:E250"/>
+    <mergeCell ref="A261:L261"/>
+    <mergeCell ref="G270:H270"/>
+    <mergeCell ref="J270:K270"/>
+    <mergeCell ref="G240:H240"/>
+    <mergeCell ref="J240:K240"/>
+    <mergeCell ref="A251:L251"/>
+    <mergeCell ref="A252:F252"/>
+    <mergeCell ref="A253:B253"/>
+    <mergeCell ref="D253:F253"/>
+    <mergeCell ref="A260:B260"/>
+    <mergeCell ref="D260:E260"/>
+    <mergeCell ref="A191:L191"/>
+    <mergeCell ref="A192:F192"/>
+    <mergeCell ref="A193:B193"/>
+    <mergeCell ref="D193:F193"/>
+    <mergeCell ref="A200:B200"/>
+    <mergeCell ref="D200:E200"/>
+    <mergeCell ref="A231:L231"/>
+    <mergeCell ref="A232:F232"/>
+    <mergeCell ref="A233:B233"/>
+    <mergeCell ref="D233:F233"/>
+    <mergeCell ref="A201:L201"/>
+    <mergeCell ref="A202:F202"/>
+    <mergeCell ref="A203:B203"/>
+    <mergeCell ref="D203:F203"/>
+    <mergeCell ref="A210:B210"/>
+    <mergeCell ref="D210:E210"/>
+    <mergeCell ref="G202:L202"/>
+    <mergeCell ref="G203:H203"/>
+    <mergeCell ref="J203:L203"/>
+    <mergeCell ref="G210:H210"/>
+    <mergeCell ref="J210:K210"/>
+    <mergeCell ref="A211:L211"/>
+    <mergeCell ref="A212:F212"/>
+    <mergeCell ref="G212:L212"/>
+    <mergeCell ref="A161:L161"/>
+    <mergeCell ref="A162:F162"/>
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="A170:B170"/>
+    <mergeCell ref="D170:E170"/>
+    <mergeCell ref="A171:L171"/>
+    <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A173:B173"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="G172:L172"/>
+    <mergeCell ref="G173:H173"/>
+    <mergeCell ref="J173:L173"/>
+    <mergeCell ref="A151:L151"/>
+    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="A153:B153"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="A160:B160"/>
+    <mergeCell ref="D160:E160"/>
+    <mergeCell ref="A141:L141"/>
+    <mergeCell ref="A142:F142"/>
+    <mergeCell ref="A143:B143"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="A150:B150"/>
+    <mergeCell ref="D150:E150"/>
+    <mergeCell ref="G152:L152"/>
+    <mergeCell ref="G153:H153"/>
+    <mergeCell ref="J153:L153"/>
+    <mergeCell ref="G160:H160"/>
+    <mergeCell ref="J160:K160"/>
+    <mergeCell ref="A131:L131"/>
+    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="D140:E140"/>
+    <mergeCell ref="A121:L121"/>
+    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="A130:B130"/>
+    <mergeCell ref="D130:E130"/>
+    <mergeCell ref="G122:L122"/>
+    <mergeCell ref="G123:H123"/>
+    <mergeCell ref="J123:L123"/>
+    <mergeCell ref="G130:H130"/>
+    <mergeCell ref="J130:K130"/>
+    <mergeCell ref="G132:L132"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="J133:L133"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="J140:K140"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="A111:L111"/>
+    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="D120:E120"/>
+    <mergeCell ref="A101:L101"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="D110:E110"/>
+    <mergeCell ref="G112:L112"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="J113:L113"/>
+    <mergeCell ref="G120:H120"/>
+    <mergeCell ref="J120:K120"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="J103:L103"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="A61:L61"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G22:L22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G92:L92"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="A71:L71"/>
+    <mergeCell ref="P270:Q270"/>
+    <mergeCell ref="M202:R202"/>
+    <mergeCell ref="M203:N203"/>
+    <mergeCell ref="P203:R203"/>
+    <mergeCell ref="M210:N210"/>
+    <mergeCell ref="P210:Q210"/>
+    <mergeCell ref="G262:L262"/>
+    <mergeCell ref="M262:R262"/>
+    <mergeCell ref="G263:H263"/>
+    <mergeCell ref="J263:L263"/>
+    <mergeCell ref="M263:N263"/>
+    <mergeCell ref="P263:R263"/>
+    <mergeCell ref="M212:R212"/>
+    <mergeCell ref="M213:N213"/>
+    <mergeCell ref="P213:R213"/>
+    <mergeCell ref="M220:N220"/>
+    <mergeCell ref="P220:Q220"/>
+    <mergeCell ref="G233:H233"/>
+    <mergeCell ref="J233:L233"/>
+    <mergeCell ref="G52:L52"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="G72:L72"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="J73:L73"/>
+    <mergeCell ref="M73:O73"/>
+    <mergeCell ref="M103:O103"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="J110:K110"/>
+    <mergeCell ref="M110:N110"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="G82:L82"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="M83:O83"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="G102:L102"/>
+    <mergeCell ref="A91:L91"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="D100:E100"/>
+    <mergeCell ref="A81:L81"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="A90:B90"/>
     <mergeCell ref="M173:O173"/>
     <mergeCell ref="M180:N180"/>
     <mergeCell ref="A280:B280"/>
@@ -13606,270 +13848,28 @@
     <mergeCell ref="D190:E190"/>
     <mergeCell ref="G180:H180"/>
     <mergeCell ref="J180:K180"/>
-    <mergeCell ref="M103:O103"/>
-    <mergeCell ref="G110:H110"/>
-    <mergeCell ref="J110:K110"/>
-    <mergeCell ref="M110:N110"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="G82:L82"/>
-    <mergeCell ref="G83:H83"/>
-    <mergeCell ref="J83:L83"/>
-    <mergeCell ref="M83:O83"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="J90:K90"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="G102:L102"/>
-    <mergeCell ref="A91:L91"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="D100:E100"/>
-    <mergeCell ref="A81:L81"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="G52:L52"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="G72:L72"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="J73:L73"/>
-    <mergeCell ref="M73:O73"/>
-    <mergeCell ref="P270:Q270"/>
-    <mergeCell ref="M202:R202"/>
-    <mergeCell ref="M203:N203"/>
-    <mergeCell ref="P203:R203"/>
-    <mergeCell ref="M210:N210"/>
-    <mergeCell ref="P210:Q210"/>
-    <mergeCell ref="G262:L262"/>
-    <mergeCell ref="M262:R262"/>
-    <mergeCell ref="G263:H263"/>
-    <mergeCell ref="J263:L263"/>
-    <mergeCell ref="M263:N263"/>
-    <mergeCell ref="P263:R263"/>
-    <mergeCell ref="M212:R212"/>
-    <mergeCell ref="M213:N213"/>
-    <mergeCell ref="P213:R213"/>
-    <mergeCell ref="M220:N220"/>
-    <mergeCell ref="P220:Q220"/>
-    <mergeCell ref="G233:H233"/>
-    <mergeCell ref="J233:L233"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G92:L92"/>
-    <mergeCell ref="G93:H93"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="J100:K100"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="A71:L71"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="A61:L61"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="A111:L111"/>
-    <mergeCell ref="A112:F112"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="A120:B120"/>
-    <mergeCell ref="D120:E120"/>
-    <mergeCell ref="A101:L101"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="D110:E110"/>
-    <mergeCell ref="G112:L112"/>
-    <mergeCell ref="G113:H113"/>
-    <mergeCell ref="J113:L113"/>
-    <mergeCell ref="G120:H120"/>
-    <mergeCell ref="J120:K120"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="J103:L103"/>
-    <mergeCell ref="A131:L131"/>
-    <mergeCell ref="A132:F132"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="A140:B140"/>
-    <mergeCell ref="D140:E140"/>
-    <mergeCell ref="A121:L121"/>
-    <mergeCell ref="A122:F122"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="A130:B130"/>
-    <mergeCell ref="D130:E130"/>
-    <mergeCell ref="G122:L122"/>
-    <mergeCell ref="G123:H123"/>
-    <mergeCell ref="J123:L123"/>
-    <mergeCell ref="G130:H130"/>
-    <mergeCell ref="J130:K130"/>
-    <mergeCell ref="G132:L132"/>
-    <mergeCell ref="G133:H133"/>
-    <mergeCell ref="J133:L133"/>
-    <mergeCell ref="G140:H140"/>
-    <mergeCell ref="J140:K140"/>
-    <mergeCell ref="A151:L151"/>
-    <mergeCell ref="A152:F152"/>
-    <mergeCell ref="A153:B153"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="A160:B160"/>
-    <mergeCell ref="D160:E160"/>
-    <mergeCell ref="A141:L141"/>
-    <mergeCell ref="A142:F142"/>
-    <mergeCell ref="A143:B143"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="A150:B150"/>
-    <mergeCell ref="D150:E150"/>
-    <mergeCell ref="G152:L152"/>
-    <mergeCell ref="G153:H153"/>
-    <mergeCell ref="J153:L153"/>
-    <mergeCell ref="G160:H160"/>
-    <mergeCell ref="J160:K160"/>
-    <mergeCell ref="A161:L161"/>
-    <mergeCell ref="A162:F162"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="A170:B170"/>
-    <mergeCell ref="D170:E170"/>
-    <mergeCell ref="A171:L171"/>
-    <mergeCell ref="A172:F172"/>
-    <mergeCell ref="A173:B173"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="G172:L172"/>
-    <mergeCell ref="G173:H173"/>
-    <mergeCell ref="J173:L173"/>
-    <mergeCell ref="A191:L191"/>
-    <mergeCell ref="A192:F192"/>
-    <mergeCell ref="A193:B193"/>
-    <mergeCell ref="D193:F193"/>
-    <mergeCell ref="A200:B200"/>
-    <mergeCell ref="D200:E200"/>
-    <mergeCell ref="A231:L231"/>
-    <mergeCell ref="A232:F232"/>
-    <mergeCell ref="A233:B233"/>
-    <mergeCell ref="D233:F233"/>
-    <mergeCell ref="A201:L201"/>
-    <mergeCell ref="A202:F202"/>
-    <mergeCell ref="A203:B203"/>
-    <mergeCell ref="D203:F203"/>
-    <mergeCell ref="A210:B210"/>
-    <mergeCell ref="D210:E210"/>
-    <mergeCell ref="G202:L202"/>
-    <mergeCell ref="G203:H203"/>
-    <mergeCell ref="J203:L203"/>
-    <mergeCell ref="G210:H210"/>
-    <mergeCell ref="J210:K210"/>
-    <mergeCell ref="A211:L211"/>
-    <mergeCell ref="A212:F212"/>
-    <mergeCell ref="G212:L212"/>
-    <mergeCell ref="A262:F262"/>
-    <mergeCell ref="A263:B263"/>
-    <mergeCell ref="D263:F263"/>
-    <mergeCell ref="A270:B270"/>
-    <mergeCell ref="D270:E270"/>
-    <mergeCell ref="A240:B240"/>
-    <mergeCell ref="D240:E240"/>
-    <mergeCell ref="A241:L241"/>
-    <mergeCell ref="A242:F242"/>
-    <mergeCell ref="A243:B243"/>
-    <mergeCell ref="D243:F243"/>
-    <mergeCell ref="A250:B250"/>
-    <mergeCell ref="D250:E250"/>
-    <mergeCell ref="A261:L261"/>
-    <mergeCell ref="G270:H270"/>
-    <mergeCell ref="J270:K270"/>
-    <mergeCell ref="G240:H240"/>
-    <mergeCell ref="J240:K240"/>
-    <mergeCell ref="A251:L251"/>
-    <mergeCell ref="A252:F252"/>
-    <mergeCell ref="A253:B253"/>
-    <mergeCell ref="D253:F253"/>
-    <mergeCell ref="A260:B260"/>
-    <mergeCell ref="D260:E260"/>
-    <mergeCell ref="G32:L32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="G42:L42"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="A213:B213"/>
-    <mergeCell ref="D213:F213"/>
-    <mergeCell ref="G213:H213"/>
-    <mergeCell ref="J213:L213"/>
-    <mergeCell ref="A220:B220"/>
-    <mergeCell ref="D220:E220"/>
-    <mergeCell ref="G220:H220"/>
-    <mergeCell ref="J220:K220"/>
-    <mergeCell ref="G232:L232"/>
-    <mergeCell ref="A221:L221"/>
-    <mergeCell ref="A222:F222"/>
-    <mergeCell ref="G222:L222"/>
-    <mergeCell ref="A223:B223"/>
-    <mergeCell ref="D223:F223"/>
-    <mergeCell ref="G223:H223"/>
-    <mergeCell ref="J223:L223"/>
-    <mergeCell ref="A230:B230"/>
-    <mergeCell ref="D230:E230"/>
-    <mergeCell ref="G230:H230"/>
-    <mergeCell ref="J230:K230"/>
+    <mergeCell ref="A281:L281"/>
+    <mergeCell ref="A282:F282"/>
+    <mergeCell ref="G282:L282"/>
+    <mergeCell ref="A283:B283"/>
+    <mergeCell ref="D283:F283"/>
+    <mergeCell ref="G283:H283"/>
+    <mergeCell ref="J283:L283"/>
+    <mergeCell ref="A290:B290"/>
+    <mergeCell ref="D290:E290"/>
+    <mergeCell ref="G290:H290"/>
+    <mergeCell ref="J290:K290"/>
+    <mergeCell ref="A291:L291"/>
+    <mergeCell ref="J300:K300"/>
+    <mergeCell ref="G300:H300"/>
+    <mergeCell ref="D300:E300"/>
+    <mergeCell ref="A300:B300"/>
+    <mergeCell ref="J293:L293"/>
+    <mergeCell ref="G293:H293"/>
+    <mergeCell ref="D293:F293"/>
+    <mergeCell ref="A293:B293"/>
+    <mergeCell ref="G292:L292"/>
+    <mergeCell ref="A292:F292"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -13935,7 +13935,7 @@
       <c r="W1" s="85"/>
     </row>
     <row r="2" spans="1:23" s="14" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="76" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="87"/>
@@ -14849,7 +14849,7 @@
       <c r="W1" s="85"/>
     </row>
     <row r="2" spans="1:23" s="14" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="76" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="87"/>
@@ -15763,7 +15763,7 @@
       <c r="W1" s="85"/>
     </row>
     <row r="2" spans="1:23" s="14" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="76" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="87"/>
